--- a/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
@@ -1472,7 +1472,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 7 progress: 1 of 122 items Done  (0.8%)</t>
+          <t>Epic 7 progress: 4 of 122 items Done  (3.3%)</t>
         </is>
       </c>
     </row>
@@ -1525,14 +1525,14 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D6" s="12" t="n">
         <v>26</v>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
@@ -2912,13 +2912,17 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I15" s="19" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I15" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J15" s="13" t="inlineStr"/>
-      <c r="K15" s="13" t="inlineStr"/>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17 as Sprint 1 batch 2 (with U7-01.26). Verified: backend /operating-score returns view='owner' with my_snapshot; SelfView renders clean with all helpers; no React console errors. OwnerView visual polish (formula panel + empty-state coaching + skeleton) components compile without errors; render-path verification blocked in preview by cookie-origin quirk (localhost vs 127.0.0.1 cookie jars), will confirm on next live deploy.</t>
+        </is>
+      </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -3016,13 +3020,17 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I17" s="19" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I17" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J17" s="13" t="inlineStr"/>
-      <c r="K17" s="13" t="inlineStr"/>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17 as Sprint 1 batch 2 (with U7-01.26). Verified: backend /operating-score returns view='owner' with my_snapshot; SelfView renders clean with all helpers; no React console errors. OwnerView visual polish (formula panel + empty-state coaching + skeleton) components compile without errors; render-path verification blocked in preview by cookie-origin quirk (localhost vs 127.0.0.1 cookie jars), will confirm on next live deploy.</t>
+        </is>
+      </c>
       <c r="L17" s="13" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -3224,13 +3232,17 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I21" s="19" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I21" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J21" s="13" t="inlineStr"/>
-      <c r="K21" s="13" t="inlineStr"/>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17 as Sprint 1 batch 2 (with U7-01.26). Verified: backend /operating-score returns view='owner' with my_snapshot; SelfView renders clean with all helpers; no React console errors. OwnerView visual polish (formula panel + empty-state coaching + skeleton) components compile without errors; render-path verification blocked in preview by cookie-origin quirk (localhost vs 127.0.0.1 cookie jars), will confirm on next live deploy.</t>
+        </is>
+      </c>
       <c r="L21" s="13" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>

--- a/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
@@ -1472,7 +1472,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 7 progress: 4 of 122 items Done  (3.3%)</t>
+          <t>Epic 7 progress: 17 of 122 items Done  (13.9%)</t>
         </is>
       </c>
     </row>
@@ -1525,14 +1525,14 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D6" s="12" t="n">
         <v>26</v>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
@@ -2236,13 +2236,17 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I2" s="19" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I2" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J2" s="13" t="inlineStr"/>
-      <c r="K2" s="13" t="inlineStr"/>
+      <c r="K2" s="13" t="inlineStr">
+        <is>
+          <t>Frontend demo shipped 2026-08-17 (Sprint 1 batch 3). Hardcoded/mock data in _operatingScoreDemo.js for: 30-day trend, week-over-week delta, per-category drivers, drill-down items, Dex narrative + explainer, suggested actions, employee deltas, weight presets. Backend wiring lands next -- each demo constant carries a comment naming the endpoint it will replace. Founder ask 2026-08-17: 'in this full system just put the implement the demo only we will wire up all the backend later. implement all the frontend part'. Zero React errors on compile; both SelfView (non-owner) and OwnerView (owner) code paths compile clean; OwnerView pixel walkthrough blocked in preview by cookie-origin quirk, founder to verify on next deploy.</t>
+        </is>
+      </c>
       <c r="L2" s="13" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -2340,13 +2344,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I4" s="19" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I4" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J4" s="13" t="inlineStr"/>
-      <c r="K4" s="13" t="inlineStr"/>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>Frontend demo shipped 2026-08-17 (Sprint 1 batch 3). Hardcoded/mock data in _operatingScoreDemo.js for: 30-day trend, week-over-week delta, per-category drivers, drill-down items, Dex narrative + explainer, suggested actions, employee deltas, weight presets. Backend wiring lands next -- each demo constant carries a comment naming the endpoint it will replace. Founder ask 2026-08-17: 'in this full system just put the implement the demo only we will wire up all the backend later. implement all the frontend part'. Zero React errors on compile; both SelfView (non-owner) and OwnerView (owner) code paths compile clean; OwnerView pixel walkthrough blocked in preview by cookie-origin quirk, founder to verify on next deploy.</t>
+        </is>
+      </c>
       <c r="L4" s="13" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -2392,13 +2400,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I5" s="19" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I5" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J5" s="13" t="inlineStr"/>
-      <c r="K5" s="13" t="inlineStr"/>
+      <c r="K5" s="13" t="inlineStr">
+        <is>
+          <t>Frontend demo shipped 2026-08-17 (Sprint 1 batch 3). Hardcoded/mock data in _operatingScoreDemo.js for: 30-day trend, week-over-week delta, per-category drivers, drill-down items, Dex narrative + explainer, suggested actions, employee deltas, weight presets. Backend wiring lands next -- each demo constant carries a comment naming the endpoint it will replace. Founder ask 2026-08-17: 'in this full system just put the implement the demo only we will wire up all the backend later. implement all the frontend part'. Zero React errors on compile; both SelfView (non-owner) and OwnerView (owner) code paths compile clean; OwnerView pixel walkthrough blocked in preview by cookie-origin quirk, founder to verify on next deploy.</t>
+        </is>
+      </c>
       <c r="L5" s="13" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -2444,13 +2456,17 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I6" s="19" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J6" s="13" t="inlineStr"/>
-      <c r="K6" s="13" t="inlineStr"/>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>Frontend demo shipped 2026-08-17 (Sprint 1 batch 3). Hardcoded/mock data in _operatingScoreDemo.js for: 30-day trend, week-over-week delta, per-category drivers, drill-down items, Dex narrative + explainer, suggested actions, employee deltas, weight presets. Backend wiring lands next -- each demo constant carries a comment naming the endpoint it will replace. Founder ask 2026-08-17: 'in this full system just put the implement the demo only we will wire up all the backend later. implement all the frontend part'. Zero React errors on compile; both SelfView (non-owner) and OwnerView (owner) code paths compile clean; OwnerView pixel walkthrough blocked in preview by cookie-origin quirk, founder to verify on next deploy.</t>
+        </is>
+      </c>
       <c r="L6" s="13" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -2496,13 +2512,17 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I7" s="19" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I7" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J7" s="13" t="inlineStr"/>
-      <c r="K7" s="13" t="inlineStr"/>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>Frontend demo shipped 2026-08-17 (Sprint 1 batch 3). Hardcoded/mock data in _operatingScoreDemo.js for: 30-day trend, week-over-week delta, per-category drivers, drill-down items, Dex narrative + explainer, suggested actions, employee deltas, weight presets. Backend wiring lands next -- each demo constant carries a comment naming the endpoint it will replace. Founder ask 2026-08-17: 'in this full system just put the implement the demo only we will wire up all the backend later. implement all the frontend part'. Zero React errors on compile; both SelfView (non-owner) and OwnerView (owner) code paths compile clean; OwnerView pixel walkthrough blocked in preview by cookie-origin quirk, founder to verify on next deploy.</t>
+        </is>
+      </c>
       <c r="L7" s="13" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -2548,13 +2568,17 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I8" s="19" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J8" s="13" t="inlineStr"/>
-      <c r="K8" s="13" t="inlineStr"/>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>Frontend demo shipped 2026-08-17 (Sprint 1 batch 3). Hardcoded/mock data in _operatingScoreDemo.js for: 30-day trend, week-over-week delta, per-category drivers, drill-down items, Dex narrative + explainer, suggested actions, employee deltas, weight presets. Backend wiring lands next -- each demo constant carries a comment naming the endpoint it will replace. Founder ask 2026-08-17: 'in this full system just put the implement the demo only we will wire up all the backend later. implement all the frontend part'. Zero React errors on compile; both SelfView (non-owner) and OwnerView (owner) code paths compile clean; OwnerView pixel walkthrough blocked in preview by cookie-origin quirk, founder to verify on next deploy.</t>
+        </is>
+      </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -2600,13 +2624,17 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I9" s="19" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J9" s="13" t="inlineStr"/>
-      <c r="K9" s="13" t="inlineStr"/>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>Frontend demo shipped 2026-08-17 (Sprint 1 batch 3). Hardcoded/mock data in _operatingScoreDemo.js for: 30-day trend, week-over-week delta, per-category drivers, drill-down items, Dex narrative + explainer, suggested actions, employee deltas, weight presets. Backend wiring lands next -- each demo constant carries a comment naming the endpoint it will replace. Founder ask 2026-08-17: 'in this full system just put the implement the demo only we will wire up all the backend later. implement all the frontend part'. Zero React errors on compile; both SelfView (non-owner) and OwnerView (owner) code paths compile clean; OwnerView pixel walkthrough blocked in preview by cookie-origin quirk, founder to verify on next deploy.</t>
+        </is>
+      </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -2652,13 +2680,17 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I10" s="19" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J10" s="13" t="inlineStr"/>
-      <c r="K10" s="13" t="inlineStr"/>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>Frontend demo shipped 2026-08-17 (Sprint 1 batch 3). Hardcoded/mock data in _operatingScoreDemo.js for: 30-day trend, week-over-week delta, per-category drivers, drill-down items, Dex narrative + explainer, suggested actions, employee deltas, weight presets. Backend wiring lands next -- each demo constant carries a comment naming the endpoint it will replace. Founder ask 2026-08-17: 'in this full system just put the implement the demo only we will wire up all the backend later. implement all the frontend part'. Zero React errors on compile; both SelfView (non-owner) and OwnerView (owner) code paths compile clean; OwnerView pixel walkthrough blocked in preview by cookie-origin quirk, founder to verify on next deploy.</t>
+        </is>
+      </c>
       <c r="L10" s="13" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -2704,13 +2736,17 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I11" s="19" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I11" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J11" s="13" t="inlineStr"/>
-      <c r="K11" s="13" t="inlineStr"/>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>Frontend demo shipped 2026-08-17 (Sprint 1 batch 3). Hardcoded/mock data in _operatingScoreDemo.js for: 30-day trend, week-over-week delta, per-category drivers, drill-down items, Dex narrative + explainer, suggested actions, employee deltas, weight presets. Backend wiring lands next -- each demo constant carries a comment naming the endpoint it will replace. Founder ask 2026-08-17: 'in this full system just put the implement the demo only we will wire up all the backend later. implement all the frontend part'. Zero React errors on compile; both SelfView (non-owner) and OwnerView (owner) code paths compile clean; OwnerView pixel walkthrough blocked in preview by cookie-origin quirk, founder to verify on next deploy.</t>
+        </is>
+      </c>
       <c r="L11" s="13" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -2756,13 +2792,17 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I12" s="19" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I12" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J12" s="13" t="inlineStr"/>
-      <c r="K12" s="13" t="inlineStr"/>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>Frontend demo shipped 2026-08-17 (Sprint 1 batch 3). Hardcoded/mock data in _operatingScoreDemo.js for: 30-day trend, week-over-week delta, per-category drivers, drill-down items, Dex narrative + explainer, suggested actions, employee deltas, weight presets. Backend wiring lands next -- each demo constant carries a comment naming the endpoint it will replace. Founder ask 2026-08-17: 'in this full system just put the implement the demo only we will wire up all the backend later. implement all the frontend part'. Zero React errors on compile; both SelfView (non-owner) and OwnerView (owner) code paths compile clean; OwnerView pixel walkthrough blocked in preview by cookie-origin quirk, founder to verify on next deploy.</t>
+        </is>
+      </c>
       <c r="L12" s="13" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -2860,13 +2900,17 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I14" s="19" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I14" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J14" s="13" t="inlineStr"/>
-      <c r="K14" s="13" t="inlineStr"/>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>Frontend demo shipped 2026-08-17 (Sprint 1 batch 3). Hardcoded/mock data in _operatingScoreDemo.js for: 30-day trend, week-over-week delta, per-category drivers, drill-down items, Dex narrative + explainer, suggested actions, employee deltas, weight presets. Backend wiring lands next -- each demo constant carries a comment naming the endpoint it will replace. Founder ask 2026-08-17: 'in this full system just put the implement the demo only we will wire up all the backend later. implement all the frontend part'. Zero React errors on compile; both SelfView (non-owner) and OwnerView (owner) code paths compile clean; OwnerView pixel walkthrough blocked in preview by cookie-origin quirk, founder to verify on next deploy.</t>
+        </is>
+      </c>
       <c r="L14" s="13" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -2968,13 +3012,17 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I16" s="19" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I16" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J16" s="13" t="inlineStr"/>
-      <c r="K16" s="13" t="inlineStr"/>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Frontend demo shipped 2026-08-17 (Sprint 1 batch 3). Hardcoded/mock data in _operatingScoreDemo.js for: 30-day trend, week-over-week delta, per-category drivers, drill-down items, Dex narrative + explainer, suggested actions, employee deltas, weight presets. Backend wiring lands next -- each demo constant carries a comment naming the endpoint it will replace. Founder ask 2026-08-17: 'in this full system just put the implement the demo only we will wire up all the backend later. implement all the frontend part'. Zero React errors on compile; both SelfView (non-owner) and OwnerView (owner) code paths compile clean; OwnerView pixel walkthrough blocked in preview by cookie-origin quirk, founder to verify on next deploy.</t>
+        </is>
+      </c>
       <c r="L16" s="13" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -3076,13 +3124,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I18" s="19" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I18" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J18" s="13" t="inlineStr"/>
-      <c r="K18" s="13" t="inlineStr"/>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>Frontend demo shipped 2026-08-17 (Sprint 1 batch 3). Hardcoded/mock data in _operatingScoreDemo.js for: 30-day trend, week-over-week delta, per-category drivers, drill-down items, Dex narrative + explainer, suggested actions, employee deltas, weight presets. Backend wiring lands next -- each demo constant carries a comment naming the endpoint it will replace. Founder ask 2026-08-17: 'in this full system just put the implement the demo only we will wire up all the backend later. implement all the frontend part'. Zero React errors on compile; both SelfView (non-owner) and OwnerView (owner) code paths compile clean; OwnerView pixel walkthrough blocked in preview by cookie-origin quirk, founder to verify on next deploy.</t>
+        </is>
+      </c>
       <c r="L18" s="13" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>

--- a/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
@@ -1472,7 +1472,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 7 progress: 17 of 122 items Done  (13.9%)</t>
+          <t>Epic 7 progress: 17 of 135 items Done  (12.6%)</t>
         </is>
       </c>
     </row>
@@ -1528,11 +1528,11 @@
         <v>17</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
@@ -2118,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L123"/>
+  <dimension ref="A1:L136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8613,6 +8613,786 @@
         </is>
       </c>
     </row>
+    <row r="124" ht="92" customHeight="1">
+      <c r="A124" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.27</t>
+        </is>
+      </c>
+      <c r="B124" s="13" t="inlineStr">
+        <is>
+          <t>OperatingScore.js + services/*</t>
+        </is>
+      </c>
+      <c r="C124" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" s="13" t="inlineStr">
+        <is>
+          <t>Backend wiring</t>
+        </is>
+      </c>
+      <c r="E124" s="13" t="inlineStr">
+        <is>
+          <t>Backend: 30-day operating-score snapshot history + daily cron</t>
+        </is>
+      </c>
+      <c r="F124" s="13" t="inlineStr">
+        <is>
+          <t>NEW COLLECTION operating_score_history: {tenant_id, date, overall, categories: {execution, finance, sales, responsiveness}, employees: [{id, score}], stats}. Daily cron writes one row per tenant per day at 03:00 IST. GET /api/operating-score-history?days=30 returns the last 30. Replaces _operatingScoreDemo.demoTrend. Starts fresh on ship day (per open decision #5 in the analysis doc); sparkline appears from day 1 as a single dot and fills out over 30 days.</t>
+        </is>
+      </c>
+      <c r="G124" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H124" s="13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I124" s="19" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J124" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.3</t>
+        </is>
+      </c>
+      <c r="K124" s="13" t="inlineStr">
+        <is>
+          <t>Wire target: HeroCard sparkline (U7-01.3 shipped as demo).</t>
+        </is>
+      </c>
+      <c r="L124" s="13" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="92" customHeight="1">
+      <c r="A125" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.28</t>
+        </is>
+      </c>
+      <c r="B125" s="13" t="inlineStr">
+        <is>
+          <t>OperatingScore.js + services/*</t>
+        </is>
+      </c>
+      <c r="C125" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" s="13" t="inlineStr">
+        <is>
+          <t>Backend wiring</t>
+        </is>
+      </c>
+      <c r="E125" s="13" t="inlineStr">
+        <is>
+          <t>Backend: week-over-week delta computation from history</t>
+        </is>
+      </c>
+      <c r="F125" s="13" t="inlineStr">
+        <is>
+          <t>Compute this_week_avg - last_week_avg from operating_score_history. Return in /api/operating-score as company.delta = {value, sign, period}. First 7 days after ship day: return null (not enough data). Replaces _operatingScoreDemo.demoDelta.</t>
+        </is>
+      </c>
+      <c r="G125" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H125" s="13" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I125" s="19" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J125" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.27</t>
+        </is>
+      </c>
+      <c r="K125" s="13" t="inlineStr">
+        <is>
+          <t>Wire target: HeroCard DeltaChip (U7-01.1 shipped as demo). Also enables per-employee deltas (U7-01.33).</t>
+        </is>
+      </c>
+      <c r="L125" s="13" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="92" customHeight="1">
+      <c r="A126" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.29</t>
+        </is>
+      </c>
+      <c r="B126" s="13" t="inlineStr">
+        <is>
+          <t>OperatingScore.js + services/*</t>
+        </is>
+      </c>
+      <c r="C126" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" s="13" t="inlineStr">
+        <is>
+          <t>Backend wiring</t>
+        </is>
+      </c>
+      <c r="E126" s="13" t="inlineStr">
+        <is>
+          <t>Backend: per-category drivers in /operating-score payload</t>
+        </is>
+      </c>
+      <c r="F126" s="13" t="inlineStr">
+        <is>
+          <t>Extend /operating-score response with drivers per category. Owner view: company.drivers = {execution: [3 items], finance: [3 items], sales: [3 items], responsiveness: [3 items]} where each driver is {label, value, tone: good|warn|bad|neutral}. Values derived from same tasks/invoices/decisions/complaints queries already in _company_operating_view -- new work is just picking the top 3 signals per category and formatting them. Replaces _operatingScoreDemo.demoDrivers.</t>
+        </is>
+      </c>
+      <c r="G126" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H126" s="13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I126" s="19" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J126" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.4</t>
+        </is>
+      </c>
+      <c r="K126" s="13" t="inlineStr">
+        <is>
+          <t>Wire target: CategoryCard drivers (U7-01.4 shipped as demo).</t>
+        </is>
+      </c>
+      <c r="L126" s="13" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="92" customHeight="1">
+      <c r="A127" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.30</t>
+        </is>
+      </c>
+      <c r="B127" s="13" t="inlineStr">
+        <is>
+          <t>OperatingScore.js + services/*</t>
+        </is>
+      </c>
+      <c r="C127" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D127" s="13" t="inlineStr">
+        <is>
+          <t>Backend wiring</t>
+        </is>
+      </c>
+      <c r="E127" s="13" t="inlineStr">
+        <is>
+          <t>Backend: category drill-down endpoint</t>
+        </is>
+      </c>
+      <c r="F127" s="13" t="inlineStr">
+        <is>
+          <t>GET /api/operating-score/drill/{category} where category in {execution, finance, sales, responsiveness}. Returns {title, hero, items: [{title, meta, tone}], action: {label, to}}. Execution: top 5 tasks by status/overdue. Finance: top 5 invoices by overdue/paid. Sales: top 5 decisions by status/latency. Responsiveness: top 5 complaints by age. Owner-only. Replaces _operatingScoreDemo.demoDrilldowns.</t>
+        </is>
+      </c>
+      <c r="G127" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H127" s="13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I127" s="19" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J127" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.5, U7-01.6, U7-01.7, U7-01.8</t>
+        </is>
+      </c>
+      <c r="K127" s="13" t="inlineStr">
+        <is>
+          <t>Wire target: CategoryDrillModal (U7-01.5..8 shipped as demo).</t>
+        </is>
+      </c>
+      <c r="L127" s="13" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="92" customHeight="1">
+      <c r="A128" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.31</t>
+        </is>
+      </c>
+      <c r="B128" s="13" t="inlineStr">
+        <is>
+          <t>OperatingScore.js + services/*</t>
+        </is>
+      </c>
+      <c r="C128" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" s="13" t="inlineStr">
+        <is>
+          <t>Backend wiring</t>
+        </is>
+      </c>
+      <c r="E128" s="13" t="inlineStr">
+        <is>
+          <t>Backend: Dex operating-score-explain AI endpoint</t>
+        </is>
+      </c>
+      <c r="F128" s="13" t="inlineStr">
+        <is>
+          <t>POST /api/ai/operating-score-explain -&gt; returns {headline: str (one sentence), explainer: str (2-3 sentences, actionable), focus: category_key}. Inputs: current scores + top drivers + week-over-week deltas. Uses claude_chat under DPDP consent gate (RBAC-25). Under quota control (FIX-005-B). Cached per-tenant for 15 min (see U7-01.36). Replaces the two _operatingScoreDemo.demoDex fields (headline + explainer). Prompt design: warm, honest, names the biggest lever + estimated point-lift.</t>
+        </is>
+      </c>
+      <c r="G128" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H128" s="13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I128" s="19" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J128" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.1, U7-01.9, RBAC-25</t>
+        </is>
+      </c>
+      <c r="K128" s="13" t="inlineStr">
+        <is>
+          <t>Wire targets: HeroCard narrative (U7-01.1) + DexExplainerCard (U7-01.9). Both shipped with hardcoded demo text.</t>
+        </is>
+      </c>
+      <c r="L128" s="13" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="92" customHeight="1">
+      <c r="A129" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.32</t>
+        </is>
+      </c>
+      <c r="B129" s="13" t="inlineStr">
+        <is>
+          <t>OperatingScore.js + services/*</t>
+        </is>
+      </c>
+      <c r="C129" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" s="13" t="inlineStr">
+        <is>
+          <t>Backend wiring</t>
+        </is>
+      </c>
+      <c r="E129" s="13" t="inlineStr">
+        <is>
+          <t>Backend: suggested-actions derivation from stats</t>
+        </is>
+      </c>
+      <c r="F129" s="13" t="inlineStr">
+        <is>
+          <t>Compute top 3 leverage points from current stats. Simple heuristic first (not AI): overdue_tasks &gt; 0 -&gt; 'Clear N overdue' with lift = min(20, N*3); open_complaints &gt; 0 -&gt; 'Resolve N complaints' with lift = min(15, N*5); waiting_decisions &gt; 0 -&gt; 'Approve N decisions' with lift = min(10, N*2); overdue_invoices &gt; 0 -&gt; 'Chase N invoices' with lift = min(12, N*3). Rank by lift desc, take top 3. Return in /operating-score as company.actions = [{label, to, icon, lift}]. Replaces _operatingScoreDemo.demoActions.</t>
+        </is>
+      </c>
+      <c r="G129" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H129" s="13" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I129" s="19" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J129" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.10</t>
+        </is>
+      </c>
+      <c r="K129" s="13" t="inlineStr">
+        <is>
+          <t>Wire target: SuggestedActions chip row (U7-01.10 shipped as demo).</t>
+        </is>
+      </c>
+      <c r="L129" s="13" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="92" customHeight="1">
+      <c r="A130" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.33</t>
+        </is>
+      </c>
+      <c r="B130" s="13" t="inlineStr">
+        <is>
+          <t>OperatingScore.js + services/*</t>
+        </is>
+      </c>
+      <c r="C130" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" s="13" t="inlineStr">
+        <is>
+          <t>Backend wiring</t>
+        </is>
+      </c>
+      <c r="E130" s="13" t="inlineStr">
+        <is>
+          <t>Backend: per-employee week-over-week delta snapshots</t>
+        </is>
+      </c>
+      <c r="F130" s="13" t="inlineStr">
+        <is>
+          <t>Extend _score_employees to also compute delta = current_score - last_week_score by reading operating_score_history[7 days ago].employees. Return per-employee: {id, name, role, score, delta}. Frontend already renders DeltaChip when delta is non-null. Replaces _operatingScoreDemo.demoEmpDeltas.</t>
+        </is>
+      </c>
+      <c r="G130" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H130" s="13" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I130" s="19" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J130" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.11, U7-01.27</t>
+        </is>
+      </c>
+      <c r="K130" s="13" t="inlineStr">
+        <is>
+          <t>Wire target: Leaderboard per-row delta (U7-01.11 shipped as demo).</t>
+        </is>
+      </c>
+      <c r="L130" s="13" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="92" customHeight="1">
+      <c r="A131" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.34</t>
+        </is>
+      </c>
+      <c r="B131" s="13" t="inlineStr">
+        <is>
+          <t>OperatingScore.js + services/*</t>
+        </is>
+      </c>
+      <c r="C131" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" s="13" t="inlineStr">
+        <is>
+          <t>Backend wiring</t>
+        </is>
+      </c>
+      <c r="E131" s="13" t="inlineStr">
+        <is>
+          <t>Backend: persist tenant.operating_score_weights</t>
+        </is>
+      </c>
+      <c r="F131" s="13" t="inlineStr">
+        <is>
+          <t>New field tenant.operating_score_weights: {execution: 35, finance: 25, sales: 20, responsiveness: 20} (default matches current hardcoded weights). PATCH /api/tenant extends to accept operating_score_weights (owner only). Weighted-average formula in _company_operating_view reads from tenant instead of hardcoded WEIGHTS dict. Validation: each weight in [0, 100], sum == 100. Frontend WeightsEditor (U7-01.17) posts here on save instead of local-only state.</t>
+        </is>
+      </c>
+      <c r="G131" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H131" s="13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I131" s="19" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J131" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.17</t>
+        </is>
+      </c>
+      <c r="K131" s="13" t="inlineStr">
+        <is>
+          <t>Wire target: FormulaExplainer weights editor (U7-01.17 shipped as demo). Also unlocks per-tenant score tuning (Manufacturer vs Services vs Distributor presets).</t>
+        </is>
+      </c>
+      <c r="L131" s="13" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="92" customHeight="1">
+      <c r="A132" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.35</t>
+        </is>
+      </c>
+      <c r="B132" s="13" t="inlineStr">
+        <is>
+          <t>OperatingScore.js + services/*</t>
+        </is>
+      </c>
+      <c r="C132" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D132" s="13" t="inlineStr">
+        <is>
+          <t>Backend wiring</t>
+        </is>
+      </c>
+      <c r="E132" s="13" t="inlineStr">
+        <is>
+          <t>Backend: wire InlineCapture to POST /api/voice-notes</t>
+        </is>
+      </c>
+      <c r="F132" s="13" t="inlineStr">
+        <is>
+          <t>InlineCapture in NotEnoughDataEmptyState currently fake-sends. Wire to existing POST /api/voice-notes with {kind: 'text', source: 'ops-empty-state', transcript: &lt;text&gt;}. Reuse existing capture pipeline (process_voice_note -&gt; ai_extract -&gt; decision creation). On success, invalidate ['operating-score'] query so the score gate flips green.</t>
+        </is>
+      </c>
+      <c r="G132" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H132" s="13" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I132" s="19" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J132" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.15</t>
+        </is>
+      </c>
+      <c r="K132" s="13" t="inlineStr">
+        <is>
+          <t>Wire target: InlineCapture form (U7-01.15 shipped as demo).</t>
+        </is>
+      </c>
+      <c r="L132" s="13" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="92" customHeight="1">
+      <c r="A133" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.36</t>
+        </is>
+      </c>
+      <c r="B133" s="13" t="inlineStr">
+        <is>
+          <t>OperatingScore.js + services/*</t>
+        </is>
+      </c>
+      <c r="C133" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" s="13" t="inlineStr">
+        <is>
+          <t>Backend wiring</t>
+        </is>
+      </c>
+      <c r="E133" s="13" t="inlineStr">
+        <is>
+          <t>Backend: cache Dex operating-score-explain per tenant 15min</t>
+        </is>
+      </c>
+      <c r="F133" s="13" t="inlineStr">
+        <is>
+          <t>Add tenant.operating_score_explain_cache = {generated_at, headline, explainer, focus, score_snapshot}. On POST /api/ai/operating-score-explain: if cache &lt; 15min old AND scores unchanged, return cached. Otherwise call Claude + store. Frontend refresh button forces cache bypass (via ?force=true query). Keeps AI cost bounded on the hot path (every owner page load).</t>
+        </is>
+      </c>
+      <c r="G133" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H133" s="13" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I133" s="19" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J133" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.31</t>
+        </is>
+      </c>
+      <c r="K133" s="13" t="inlineStr">
+        <is>
+          <t>Companion to U7-01.31 -- ship together to keep cost bounded.</t>
+        </is>
+      </c>
+      <c r="L133" s="13" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="92" customHeight="1">
+      <c r="A134" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.37</t>
+        </is>
+      </c>
+      <c r="B134" s="13" t="inlineStr">
+        <is>
+          <t>OperatingScore.js + services/*</t>
+        </is>
+      </c>
+      <c r="C134" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" s="13" t="inlineStr">
+        <is>
+          <t>Backend wiring</t>
+        </is>
+      </c>
+      <c r="E134" s="13" t="inlineStr">
+        <is>
+          <t>Phase B: better metric formulas (from analysis doc)</t>
+        </is>
+      </c>
+      <c r="F134" s="13" t="inlineStr">
+        <is>
+          <t>The analysis doc's Phase B formula upgrades, batched. Execution: add first_pass_yield (% of done tasks NOT reopened within 7 days) + plan_adoption (% of tasks with accepted execution plan, from compute_employee_stats) + proof_upload_rate (already computed for IC, surface at company level). Finance: add days_sales_outstanding (avg age of unpaid invoices) + expense_ratio_trend (30-day rolling). Sales: add decision_latency (median hours capture -&gt; approved). Responsiveness: SPLIT into complaint_response_time (median hours raised -&gt; first response) as its own metric, and remove task overdue penalty (that's execution's job already). Founder review before coding formulas -- Phase B open decision #4 in the analysis doc.</t>
+        </is>
+      </c>
+      <c r="G134" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H134" s="13" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I134" s="19" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J134" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.29, docs/Epic7_Sprint1_OperatingScore_Analysis.md</t>
+        </is>
+      </c>
+      <c r="K134" s="13" t="inlineStr">
+        <is>
+          <t>This is the analysis doc's Phase B in one item. Needs founder sign-off on formula shapes before implementation -- open decision #4.</t>
+        </is>
+      </c>
+      <c r="L134" s="13" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="92" customHeight="1">
+      <c r="A135" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.38</t>
+        </is>
+      </c>
+      <c r="B135" s="13" t="inlineStr">
+        <is>
+          <t>OperatingScore.js + services/*</t>
+        </is>
+      </c>
+      <c r="C135" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" s="13" t="inlineStr">
+        <is>
+          <t>Backend wiring</t>
+        </is>
+      </c>
+      <c r="E135" s="13" t="inlineStr">
+        <is>
+          <t>Backend: weekly snapshot email to owner (cron + template)</t>
+        </is>
+      </c>
+      <c r="F135" s="13" t="inlineStr">
+        <is>
+          <t>Owner-opt-in weekly digest email. Setting: tenant.owner_prefs.weekly_ops_email = true. Cron every Monday 09:00 IST: for each opt-in tenant, compose HTML email with score + delta + Dex 2-sentence narrative + top 3 actions. Uses existing SES/SendGrid provider (whichever S3-01 landed on). Skip if score unchanged in 7 days.</t>
+        </is>
+      </c>
+      <c r="G135" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H135" s="13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I135" s="19" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J135" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.24, U7-01.27</t>
+        </is>
+      </c>
+      <c r="K135" s="13" t="inlineStr">
+        <is>
+          <t>Wire target: U7-01.24 (frontend for the setting toggle + email template). Requires an email provider chosen and quota tracked.</t>
+        </is>
+      </c>
+      <c r="L135" s="13" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="92" customHeight="1">
+      <c r="A136" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.39</t>
+        </is>
+      </c>
+      <c r="B136" s="13" t="inlineStr">
+        <is>
+          <t>OperatingScore.js + services/*</t>
+        </is>
+      </c>
+      <c r="C136" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" s="13" t="inlineStr">
+        <is>
+          <t>Backend wiring</t>
+        </is>
+      </c>
+      <c r="E136" s="13" t="inlineStr">
+        <is>
+          <t>Backend: shareable public one-pager endpoint (signed link)</t>
+        </is>
+      </c>
+      <c r="F136" s="13" t="inlineStr">
+        <is>
+          <t>GET /public/operating-score/{token} where token is a signed JWT with tenant_id + owner_id + exp (30 days). Returns aggregated score + trend + 4 categories + Dex narrative. No employee names (aggregated only). No login required. Owner generates the link from Settings &gt; Business with 'Share company score' button; can revoke by regenerating.</t>
+        </is>
+      </c>
+      <c r="G136" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H136" s="13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I136" s="19" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J136" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.25, U7-01.27</t>
+        </is>
+      </c>
+      <c r="K136" s="13" t="inlineStr">
+        <is>
+          <t>Wire target: U7-01.25 (frontend share page + generator UI). Board-of-directors friendly one-pager, no auth needed.</t>
+        </is>
+      </c>
+      <c r="L136" s="13" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
@@ -1472,7 +1472,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 7 progress: 17 of 135 items Done  (12.6%)</t>
+          <t>Epic 7 progress: 18 of 136 items Done  (13.2%)</t>
         </is>
       </c>
     </row>
@@ -1525,14 +1525,14 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
@@ -2118,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L136"/>
+  <dimension ref="A1:L137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9393,6 +9393,66 @@
         </is>
       </c>
     </row>
+    <row r="137" ht="92" customHeight="1">
+      <c r="A137" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.40</t>
+        </is>
+      </c>
+      <c r="B137" s="13" t="inlineStr">
+        <is>
+          <t>OperatingScore.js, /api/operating-score</t>
+        </is>
+      </c>
+      <c r="C137" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" s="13" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="E137" s="13" t="inlineStr">
+        <is>
+          <t>Owner drills into teammate's full ops view (view-as)</t>
+        </is>
+      </c>
+      <c r="F137" s="13" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17: 'from the owner side if i click the team member is it working better or not will show their tasks all the things the individual ops has right'. Answer was NO -- leaderboard clicks went to /coach (WorkCoach) which shows only stats + AI review, no open work list, no active workflows, no peer context. Now: leaderboard click routes to /operating-score?user=X. Backend accepts ?user_id=X (owner-only, non-owners 403). Endpoint returns the target's full self-view payload plus view_as: {id, name, role} metadata so the frontend can render a 'Viewing &lt;name&gt; · &lt;role&gt; [Back to company view]' breadcrumb + a header shift ('X's operating view' instead of 'Hi X'). Owner still has a separate Coach affordance per row for jumping straight to AI coaching. Verified live: Meera drills into Sunita -&gt; sees her 5 open tasks + workflows + stats + Dex explainer. Privacy: Priya tries to drill into Sunita -&gt; 403 as designed.</t>
+        </is>
+      </c>
+      <c r="G137" s="13" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H137" s="13" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I137" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J137" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.26 (role split), U7-01.11 (leaderboard)</t>
+        </is>
+      </c>
+      <c r="K137" s="13" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17 as Sprint 1 batch 4. 4 new pytest guards (view-as accepted, owner-only 403, view_as metadata present) all green -- 8/8 in test_operating_score_role_split.py. Frontend: OperatingScore.js reads ?user=X via useSearchParams; ViewAsBanner shown at top of SelfView when view_as is set; leaderboard rows now link to /operating-score?user=X (was /coach?user=X); Coach kept as secondary affordance so owner can still jump straight to WorkCoach.</t>
+        </is>
+      </c>
+      <c r="L137" s="13" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
@@ -1472,7 +1472,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 7 progress: 18 of 136 items Done  (13.2%)</t>
+          <t>Epic 7 progress: 22 of 138 items Done  (15.9%)</t>
         </is>
       </c>
     </row>
@@ -1657,19 +1657,19 @@
         </is>
       </c>
       <c r="C10" s="17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="G10" s="18" t="inlineStr">
@@ -2118,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L137"/>
+  <dimension ref="A1:L139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4588,13 +4588,17 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I46" s="19" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I46" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J46" s="18" t="inlineStr"/>
-      <c r="K46" s="18" t="inlineStr"/>
+      <c r="K46" s="18" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17 (Sprint 5 batch 1). TaskCard collapses to a summary row by default -- title + priority + status pill + due-date OR OVERDUE (red stripe on card + red badge). Stage chip becomes a tiny inline pill in the summary; full workflow chip lives in the expanded body. Click any row toggles expand; other cards stay collapsed. Verified live: Priya's 4 sales tasks render as 4 clean rows, expand-in-place shows full detail (due, progress, actions, plan, trail). Highlighted cards (deep-link focus) auto-expand.</t>
+        </is>
+      </c>
       <c r="L46" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -4640,13 +4644,17 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I47" s="19" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I47" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J47" s="16" t="inlineStr"/>
-      <c r="K47" s="16" t="inlineStr"/>
+      <c r="K47" s="16" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17 (Sprint 5 batch 1). TaskCard collapses to a summary row by default -- title + priority + status pill + due-date OR OVERDUE (red stripe on card + red badge). Stage chip becomes a tiny inline pill in the summary; full workflow chip lives in the expanded body. Click any row toggles expand; other cards stay collapsed. Verified live: Priya's 4 sales tasks render as 4 clean rows, expand-in-place shows full detail (due, progress, actions, plan, trail). Highlighted cards (deep-link focus) auto-expand.</t>
+        </is>
+      </c>
       <c r="L47" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -9450,6 +9458,126 @@
       <c r="L137" s="13" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="80" customHeight="1">
+      <c r="A138" s="18" t="inlineStr">
+        <is>
+          <t>U7-05.7</t>
+        </is>
+      </c>
+      <c r="B138" s="18" t="inlineStr">
+        <is>
+          <t>MyWork.js</t>
+        </is>
+      </c>
+      <c r="C138" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D138" s="18" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="E138" s="18" t="inlineStr">
+        <is>
+          <t>AI Priority button owner-only</t>
+        </is>
+      </c>
+      <c r="F138" s="18" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17: 'ai priority also right only for owner got it'. The ranker is a whole-team judgment tool -- for an IC it hides which of their tasks they picked to work on based on someone else's AI score. Wrapped the AI Priority toggle in `isOwner` so ICs never see it. Also does not fetch /tasks/prioritize for non-owners.</t>
+        </is>
+      </c>
+      <c r="G138" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H138" s="18" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I138" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J138" s="18" t="inlineStr">
+        <is>
+          <t>U7-05.1, U7-05.2</t>
+        </is>
+      </c>
+      <c r="K138" s="18" t="inlineStr">
+        <is>
+          <t>Verified live: Sales (Priya) view shows New Task / My Work / Workflows / Leave -- no AI Priority chip. Owner still gets it.</t>
+        </is>
+      </c>
+      <c r="L138" s="18" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="80" customHeight="1">
+      <c r="A139" s="16" t="inlineStr">
+        <is>
+          <t>U7-05.8</t>
+        </is>
+      </c>
+      <c r="B139" s="16" t="inlineStr">
+        <is>
+          <t>MyWork.js</t>
+        </is>
+      </c>
+      <c r="C139" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D139" s="16" t="inlineStr">
+        <is>
+          <t>Interaction</t>
+        </is>
+      </c>
+      <c r="E139" s="16" t="inlineStr">
+        <is>
+          <t>Replace window.prompt() for reject + clarify with real Dialog</t>
+        </is>
+      </c>
+      <c r="F139" s="16" t="inlineStr">
+        <is>
+          <t>Anti-pattern cleanup. rejectTask() and clarifyTask() previously used window.prompt() which (a) blocks the browser thread, (b) returns null in some embed contexts and looks like a silent no-op (FUP-49 hit the same pattern for confirm and fixed it there), (c) has no room for helpful placeholder text or context. Now: openReasonDialog() opens a proper Dialog with a textarea, contextual placeholder ('e.g. Please add unit prices per line item.'), disabled-during-submit state, and a cancel button. Clarify requires text; reject accepts empty (matches backend contract). Shared by both actions to keep the dialog reusable.</t>
+        </is>
+      </c>
+      <c r="G139" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H139" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I139" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J139" s="16" t="inlineStr">
+        <is>
+          <t>U7-05.1</t>
+        </is>
+      </c>
+      <c r="K139" s="16" t="inlineStr">
+        <is>
+          <t>Anti-pattern was inconsistent with the rest of the app which uses Dialog for all reason capture. Approve+Reject+Clarify approver actions now all use the same interaction model.</t>
+        </is>
+      </c>
+      <c r="L139" s="16" t="inlineStr">
+        <is>
+          <t>Own audit 2026-08-17</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
@@ -1472,7 +1472,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 7 progress: 22 of 138 items Done  (15.9%)</t>
+          <t>Epic 7 progress: 26 of 138 items Done  (18.8%)</t>
         </is>
       </c>
     </row>
@@ -1657,19 +1657,19 @@
         </is>
       </c>
       <c r="C10" s="17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D10" s="17" t="n">
         <v>8</v>
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G10" s="18" t="inlineStr">
@@ -4700,13 +4700,17 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I48" s="19" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I48" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J48" s="18" t="inlineStr"/>
-      <c r="K48" s="18" t="inlineStr"/>
+      <c r="K48" s="18" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17 (Sprint 5 batch 2). Bulk select + action bar. Each TaskCard summary row now has a checkbox (outside the expand button so click doesn't toggle the card). Selecting 1+ tasks reveals a sticky bulk-action bar at the top of the list: 'N selected · Complete N · Reassign · Clear'. Complete applies status=done to all selected non-terminal tasks (Promise.all of PATCH calls). Reassign opens a dialog to pick assignee_id OR assignee_role, then applies the patch to all selected. Selection clears on scope/tab/view change. Backend batch endpoint tracked separately in Sprint 5 backlog.</t>
+        </is>
+      </c>
       <c r="L48" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -4752,13 +4756,17 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I49" s="19" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I49" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J49" s="16" t="inlineStr"/>
-      <c r="K49" s="16" t="inlineStr"/>
+      <c r="K49" s="16" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17 (Sprint 5 batch 2). PriorityScoreBars now carries per-bar tooltips via native title attribute: Impact ('customer weight, workflow blockage, cross-team deps'), Revenue ('unpaid, overdue, deal value'), Risk ('complaints, compliance, penalties'), Urgency ('overdue days, hours-to-due, escalation'). Plus the overall priority_score has 'weighted mix of four signals below' tooltip. Users can hover any label to understand what drove the number.</t>
+        </is>
+      </c>
       <c r="L49" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -4804,13 +4812,17 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I50" s="19" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I50" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J50" s="18" t="inlineStr"/>
-      <c r="K50" s="18" t="inlineStr"/>
+      <c r="K50" s="18" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17 (Sprint 5 batch 2). scope + tab + aiPriority persist in localStorage per tenant+user (key: mywork-prefs-&lt;tid&gt;-&lt;uid&gt;). Reload the page, come back tomorrow, navigate away and back -- same filters. Guarded on prefsKey so pre-login / test contexts stay no-op. Founder ask: 'remove the uneasy UX' -- resetting to 'All / Mine / no AI' every navigation was frustrating for someone who works in one category.</t>
+        </is>
+      </c>
       <c r="L50" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -4856,13 +4868,17 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I51" s="19" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I51" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J51" s="16" t="inlineStr"/>
-      <c r="K51" s="16" t="inlineStr"/>
+      <c r="K51" s="16" t="inlineStr">
+        <is>
+          <t>Verified 2026-08-17 (Sprint 5 batch 2). MyWorkMobile.jsx (MPWA-08) already uses card-plus-sheet pattern (rows collapse to 3 lines, expand to sheet), so density parity holds without new changes. Only gap: AI Priority button was visible to non-owners on mobile too -- gated on isOwner to match desktop. Full bulk-actions + filter persistence for mobile deferred (mobile has its own UX pattern for these -- backlog item).</t>
+        </is>
+      </c>
       <c r="L51" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>

--- a/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
@@ -1472,7 +1472,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 7 progress: 26 of 138 items Done  (18.8%)</t>
+          <t>Epic 7 progress: 32 of 141 items Done  (22.7%)</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L139"/>
+  <dimension ref="A1:L142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5290,11 +5290,15 @@
       </c>
       <c r="I59" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J59" s="16" t="inlineStr"/>
-      <c r="K59" s="16" t="inlineStr"/>
+      <c r="K59" s="16" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17 (commit eeca877 -- CRM Batch 2). Killed 6 "nothing here" placeholder sections via new hideWhenEmpty prop on Section. AI Relationship Intelligence card collapsed to a compact inline prompt when unscored (was a huge empty card). Deduped invoices/payments/complaints/workflows by id so the backend duplicate-return no longer double-renders. "Back to People" -&gt; "Back to CRM" now routes to /crm.</t>
+        </is>
+      </c>
       <c r="L59" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -5446,11 +5450,15 @@
       </c>
       <c r="I62" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J62" s="18" t="inlineStr"/>
-      <c r="K62" s="18" t="inlineStr"/>
+      <c r="K62" s="18" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17 (commit eeca877 -- CRM Batch 1). Card density fixed: 11+ elements per card collapsed to 5 (name + status dot + one type chip + lifecycle chip + one key signal + touched-ago). Chips use tenant lexicon (L.customer_singular / L.vendor_singular) so BUYER/SUPPLIER match everywhere. Whole card is click-target -- redundant per-card 360deg icon killed.</t>
+        </is>
+      </c>
       <c r="L62" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -6174,11 +6182,15 @@
       </c>
       <c r="I76" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J76" s="18" t="inlineStr"/>
-      <c r="K76" s="18" t="inlineStr"/>
+      <c r="K76" s="18" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17 (commits b7cd6ee + 349a7b4 + this push -- U7-09.TEAM/PEOPLE). Team is now a viewable-by-all HRM roster with click-through profile dialog and no attendance concerns (killed the attendance-portal framing). People became a three-tab admin page (Employees / Customers / Vendors) with per-tab edit gating: team_manage for Employees, "people" perm for Customers+Vendors. Every user sees the roster; owner + perm-holders keep edit affordances.</t>
+        </is>
+      </c>
       <c r="L76" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -9594,6 +9606,174 @@
       <c r="L139" s="16" t="inlineStr">
         <is>
           <t>Own audit 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="70" customHeight="1">
+      <c r="A140" s="16" t="inlineStr">
+        <is>
+          <t>U7-07.7</t>
+        </is>
+      </c>
+      <c r="B140" s="16" t="inlineStr">
+        <is>
+          <t>CRM.js, Contacts.js, ContactProfile.js</t>
+        </is>
+      </c>
+      <c r="C140" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D140" s="15" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="E140" s="16" t="inlineStr">
+        <is>
+          <t>CRM scope simplified to Buyers | Suppliers only</t>
+        </is>
+      </c>
+      <c r="F140" s="16" t="inlineStr">
+        <is>
+          <t>Old header carried 5 chips: All / Customers / Suppliers / Mine / With complaints. Founder ask: each user works in one lane at a time; complaints are already visible via the red pill on every card (Batch 1) so a dedicated tab is redundant. Reduce to two big HRM-style segmented tabs -- Buyers | Suppliers -- with count badges; move search/status/sort to a subtler filter strip below the tabs.</t>
+        </is>
+      </c>
+      <c r="G140" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H140" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I140" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J140" s="16" t="n"/>
+      <c r="K140" s="16" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17 (commit a1498ed). SCOPES trimmed from 5 to 2. Killed the useEffect that force-flipped scope to "complaints" on ?complaint=open deep-link (Desk Trends still lands on Buyers; users spot the red pills). Default scope = customers.</t>
+        </is>
+      </c>
+      <c r="L140" s="16" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="70" customHeight="1">
+      <c r="A141" s="16" t="inlineStr">
+        <is>
+          <t>U7-07.8</t>
+        </is>
+      </c>
+      <c r="B141" s="16" t="inlineStr">
+        <is>
+          <t>CRM.js, Contacts.js, ContactProfile.js</t>
+        </is>
+      </c>
+      <c r="C141" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D141" s="15" t="inlineStr">
+        <is>
+          <t>Interaction</t>
+        </is>
+      </c>
+      <c r="E141" s="16" t="inlineStr">
+        <is>
+          <t>Add-contact flow -- menu + dialog polish</t>
+        </is>
+      </c>
+      <c r="F141" s="16" t="inlineStr">
+        <is>
+          <t>Header dropdown was &lt;details&gt;/&lt;summary&gt; with cramped label-mono subtitles that read as jumbled uppercase labels ("BUYER / RETAIL, ACCOUNT / DEALER"). Dialog behind it was 10 fields dumped into a 2-col grid with no hierarchy. Rebuild: controlled menu with a Phosphor icon per option, wider (300px), normal-case helper text, backdrop click + Escape to close. Dialog: segmented CUSTOMER/DEALER/SUPPLIER tabs, auto-focused name, sectioned layout (Identity / Contact / Classification), advanced fields (GSTIN, address, tags, owner, notes) collapsed behind "More details" toggle.</t>
+        </is>
+      </c>
+      <c r="G141" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H141" s="16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I141" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J141" s="16" t="n"/>
+      <c r="K141" s="16" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17 (this push). Backdrop pattern (not document.mousedown) avoids a race with React 18 Strict Mode dev-only double-invocation that was closing the menu on the same click that opened it. Advanced section auto-expands when editing an existing contact so nothing looks missing.</t>
+        </is>
+      </c>
+      <c r="L141" s="16" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="70" customHeight="1">
+      <c r="A142" s="16" t="inlineStr">
+        <is>
+          <t>U7-10.6</t>
+        </is>
+      </c>
+      <c r="B142" s="16" t="inlineStr">
+        <is>
+          <t>Team.js, People.js, WorkCoach.js</t>
+        </is>
+      </c>
+      <c r="C142" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D142" s="15" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="E142" s="16" t="inlineStr">
+        <is>
+          <t>Team page redesign -- HRM roster + click-through profile</t>
+        </is>
+      </c>
+      <c r="F142" s="16" t="inlineStr">
+        <is>
+          <t>Team page read as an attendance portal (present/absent chips, day toggle, roster as a flat list). Founder ask: this is not attendance; make it feel like an HRM tool. Killed attendance entirely (removed /attendance useQuery + toggleAbsent). Roster is now a card grid grouped by role, with a subtle status dot (active green / pending amber / suspended gray) sourced from invite_status. Clicking a card opens a profile dialog carrying contact info + access controls -- access moved INSIDE the card so perm-holders can grant/edit from there.</t>
+        </is>
+      </c>
+      <c r="G142" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H142" s="16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I142" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J142" s="16" t="n"/>
+      <c r="K142" s="16" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17 (commit 349a7b4). Everyone sees the roster (perm gate dropped in App.js -- &lt;Protected&gt; replaces &lt;Protected perms={{team_manage}}&gt;). Non-perm-holders see the roster read-only; team_manage/owner see edit affordances.</t>
+        </is>
+      </c>
+      <c r="L142" s="16" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
@@ -1472,7 +1472,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 7 progress: 32 of 141 items Done  (22.7%)</t>
+          <t>Epic 7 progress: 33 of 142 items Done  (23.2%)</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L142"/>
+  <dimension ref="A1:L143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9777,6 +9777,62 @@
         </is>
       </c>
     </row>
+    <row r="143" ht="70" customHeight="1">
+      <c r="A143" s="18" t="inlineStr">
+        <is>
+          <t>U7-05.10</t>
+        </is>
+      </c>
+      <c r="B143" s="18" t="inlineStr">
+        <is>
+          <t>MyWork.js, i18n.js</t>
+        </is>
+      </c>
+      <c r="C143" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D143" s="17" t="inlineStr">
+        <is>
+          <t>Copy</t>
+        </is>
+      </c>
+      <c r="E143" s="18" t="inlineStr">
+        <is>
+          <t>MyWork view toggle -- "My Work" duplicates the page title</t>
+        </is>
+      </c>
+      <c r="F143" s="18" t="inlineStr">
+        <is>
+          <t>The desktop MyWork toolbar had a view toggle labeled "MY WORK" that sat next to WORKFLOWS and LEAVE. But the page itself is also called "My Work" (sidebar nav + PageHeader eyebrow/title). Owner ask: "In the owner access of work section, my we are showing my work 2 times". Rename the view toggle to TASKS across en/hi/ta so the trio reads TASKS / WORKFLOWS / LEAVE and the page-title "My Work" only appears once in the viewport. Mobile MyWorkMobile already used "Tasks" for this toggle -- desktop was the outlier.</t>
+        </is>
+      </c>
+      <c r="G143" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H143" s="18" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I143" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J143" s="18" t="n"/>
+      <c r="K143" s="18" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17 (single-line i18n change). Only the view-toggle label changes; view_mywork translation key kept for compatibility.</t>
+        </is>
+      </c>
+      <c r="L143" s="18" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
@@ -1472,7 +1472,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 7 progress: 33 of 142 items Done  (23.2%)</t>
+          <t>Epic 7 progress: 35 of 144 items Done  (24.3%)</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L143"/>
+  <dimension ref="A1:L145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9833,6 +9833,118 @@
         </is>
       </c>
     </row>
+    <row r="144" ht="70" customHeight="1">
+      <c r="A144" s="18" t="inlineStr">
+        <is>
+          <t>U7-05.11</t>
+        </is>
+      </c>
+      <c r="B144" s="18" t="inlineStr">
+        <is>
+          <t>MyWork.js</t>
+        </is>
+      </c>
+      <c r="C144" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D144" s="17" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="E144" s="18" t="inlineStr">
+        <is>
+          <t>Remove Tasks view toggle for owner (redundant with MY TASKS)</t>
+        </is>
+      </c>
+      <c r="F144" s="18" t="inlineStr">
+        <is>
+          <t>Owner ask: "remove the Tasks got it .. lets have only the my tasks, all tasks, ai priority, workflow and leave". Desktop MyWork toolbar had a TASKS button next to WORKFLOWS and LEAVE, but for owner the MY TASKS / ALL TASKS / AI PRIORITY buttons already route to view=mywork on click. TASKS sat unused. Non-owners keep the button because they lack MY TASKS / ALL TASKS and need a path back from Workflows / Leave.</t>
+        </is>
+      </c>
+      <c r="G144" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H144" s="18" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I144" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J144" s="18" t="n"/>
+      <c r="K144" s="18" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17. Follows U7-05.10 (label rename) as the second half of the owner-toolbar cleanup.</t>
+        </is>
+      </c>
+      <c r="L144" s="18" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="70" customHeight="1">
+      <c r="A145" s="18" t="inlineStr">
+        <is>
+          <t>U7-06.4</t>
+        </is>
+      </c>
+      <c r="B145" s="18" t="inlineStr">
+        <is>
+          <t>Workflows.js</t>
+        </is>
+      </c>
+      <c r="C145" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D145" s="17" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="E145" s="18" t="inlineStr">
+        <is>
+          <t>Show every operational pipeline, not only ones with data</t>
+        </is>
+      </c>
+      <c r="F145" s="18" t="inlineStr">
+        <is>
+          <t>U7-06.1 hid pipeline chips with zero live workflows -- the thinking was "cleaner strip", but a tenant that had never shipped a Procurement flow saw Procurement disappear entirely, reading as "this system does not support procurement". Founder ask: "in the workflow section lets show the complete operational, not only data workflow which has the data". Revert the empty-filter so all pipelines defined in the ops model render every time. Zero-count chips already read muted via label-mono text-muted-foreground so live pipelines still dominate visually.</t>
+        </is>
+      </c>
+      <c r="G145" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H145" s="18" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I145" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J145" s="18" t="n"/>
+      <c r="K145" s="18" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17. Verified on Sharma tenant: 6 pipelines (Distribution / Production / Procurement / Order Fulfillment / Raw Material Procurement / Production Planning) all render, with only Distribution carrying a live workflow (count=1).</t>
+        </is>
+      </c>
+      <c r="L145" s="18" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
@@ -1472,7 +1472,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 7 progress: 35 of 144 items Done  (24.3%)</t>
+          <t>Epic 7 progress: 36 of 145 items Done  (24.8%)</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L145"/>
+  <dimension ref="A1:L146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9945,6 +9945,62 @@
         </is>
       </c>
     </row>
+    <row r="146" ht="70" customHeight="1">
+      <c r="A146" s="18" t="inlineStr">
+        <is>
+          <t>U7-08.1</t>
+        </is>
+      </c>
+      <c r="B146" s="18" t="inlineStr">
+        <is>
+          <t>Ledger.js (RevenueTab)</t>
+        </is>
+      </c>
+      <c r="C146" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D146" s="17" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="E146" s="18" t="inlineStr">
+        <is>
+          <t>Revenue invoices -- overdue flag, status filter, sort, better copy</t>
+        </is>
+      </c>
+      <c r="F146" s="18" t="inlineStr">
+        <is>
+          <t>Flat 5-column table shipped as a v1; founder ask this session: audit the invoices UI/UX and fix. Six issues found and shipped: (1) no overdue signal on a 2-month-old AWAITING invoice, (2) no status filter or sort control, (3) invoice # hidden when title exists so customers had no reference to quote back on WhatsApp, (4) empty state read "No income yet" under a "Sales &amp; Service Invoices" heading, (5) Received KPI missing green accent while Billed had one -- inconsistent, (6) no roll-up total for the filtered view. Now: red overdue callout under the KPI strip (30d rule, MSME Net-30 convention); status filter chips including a red Overdue chip; sort dropdown (newest/oldest/amount/oldest-awaiting); invoice # shown inline with title; per-row red-tint + "Nd overdue" chip on overdue rows; filtered subtotal in a bold footer row.</t>
+        </is>
+      </c>
+      <c r="G146" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H146" s="18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I146" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J146" s="18" t="n"/>
+      <c r="K146" s="18" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17. Verified on Sharma tenant: 5 invoices, 1 overdue (Krishna Garments, 64d). Overdue callout + filter + row tint + chip all render correctly. Sort dropdown carries 4 options. Received KPI now green to match Billed. Old "For / Invoice" column header renamed to "Invoice" since the column now leads with #.</t>
+        </is>
+      </c>
+      <c r="L146" s="18" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
@@ -1472,7 +1472,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 7 progress: 36 of 145 items Done  (24.8%)</t>
+          <t>Epic 7 progress: 37 of 146 items Done  (25.3%)</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L146"/>
+  <dimension ref="A1:L147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10001,6 +10001,62 @@
         </is>
       </c>
     </row>
+    <row r="147" ht="70" customHeight="1">
+      <c r="A147" s="18" t="inlineStr">
+        <is>
+          <t>U7-08.2</t>
+        </is>
+      </c>
+      <c r="B147" s="18" t="inlineStr">
+        <is>
+          <t>Ledger.js</t>
+        </is>
+      </c>
+      <c r="C147" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D147" s="17" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="E147" s="18" t="inlineStr">
+        <is>
+          <t>Remove Fix Old Purchases button from Finance header</t>
+        </is>
+      </c>
+      <c r="F147" s="18" t="inlineStr">
+        <is>
+          <t>Owner ask: "remove the Fix old purchases button". The button ran /ledger/reclassify-purchases -- an AI re-classification pass on historical purchase bills. The new capture pipeline already runs classification on every bill at ingest, so the manual re-run has become admin tooling, not day-to-day owner workflow. Removed the button + its useState + handler from Ledger.js. Mobile keeps its own affordance ("Recheck earlier bills" in FinanceMobile.jsx) and the /ledger/reclassify-purchases endpoint stays live so an admin can trigger it if needed.</t>
+        </is>
+      </c>
+      <c r="G147" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H147" s="18" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I147" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J147" s="18" t="n"/>
+      <c r="K147" s="18" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17. Verified: desktop Finance header now reads OVERVIEW  REVENUE  EXPENSES  ASSETS  INVENTORY  INBOX  + ADD INCOME -- no Fix Old Purchases button.</t>
+        </is>
+      </c>
+      <c r="L147" s="18" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
@@ -1472,7 +1472,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 7 progress: 37 of 146 items Done  (25.3%)</t>
+          <t>Epic 7 progress: 38 of 147 items Done  (25.9%)</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L147"/>
+  <dimension ref="A1:L148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10057,6 +10057,62 @@
         </is>
       </c>
     </row>
+    <row r="148" ht="70" customHeight="1">
+      <c r="A148" s="16" t="inlineStr">
+        <is>
+          <t>U7-11.1</t>
+        </is>
+      </c>
+      <c r="B148" s="16" t="inlineStr">
+        <is>
+          <t>Settings.js, CompanyDetails.js</t>
+        </is>
+      </c>
+      <c r="C148" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D148" s="15" t="inlineStr">
+        <is>
+          <t>Copy + IA</t>
+        </is>
+      </c>
+      <c r="E148" s="16" t="inlineStr">
+        <is>
+          <t>Settings audit -- URL persistence, tech-bleed copy, naming collision, header casing</t>
+        </is>
+      </c>
+      <c r="F148" s="16" t="inlineStr">
+        <is>
+          <t>Owner ask: "lets work on the settings change complete it now, check and validation the UI/UX check which are things missing out and which things can be optimized". Full audit of the 4-tab layout (Business / Operations / Money / Account). Six issues found and shipped: (1) active tab did not persist in URL -- reload, back/forward and deep-links all landed on Business, (2) "WA_TENANT_ID env variable" dev copy leaked into the Workspace ID block on Business, (3) Business tab had a section called "Operating System" that collided semantically with the OPERATIONS tab (two things called Operating... doing different work), (4) two SAVE buttons on the Business card (Save operating system + Save changes) were both vague about scope, (5) MoneyAndApprovals card header used `tracking-tight` lowercase-looking treatment while every other Settings card used `uppercase font-extrabold`, (6) Money tab showed the long Finance Categories list BEFORE the two decisions that actually matter (currency + high-value threshold).</t>
+        </is>
+      </c>
+      <c r="G148" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H148" s="16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I148" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J148" s="16" t="n"/>
+      <c r="K148" s="16" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17. Fixes: (1) ?tab= URL param + back/forward sync (mirrors the Finance tab pattern), (2) Workspace ID relabeled "WhatsApp workspace code" with owner-friendly helper text -- no env-var mention, (3) "Operating System" section renamed "Rules &amp; templates" with a helper line pointing pipeline config to the Operations tab, (4) SAVE buttons relabeled by scope ("Save rules &amp; templates" + "Save company details"), (5) MoneyAndApprovals header now uppercase, (6) Money tab reordered -- Approvals first, Categories second. Bonus: Account tab desc dropped the "sessions" promise since no sessions UI exists; Business tab desc trimmed to match the renamed section.</t>
+        </is>
+      </c>
+      <c r="L148" s="16" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
@@ -1472,7 +1472,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 7 progress: 38 of 147 items Done  (25.9%)</t>
+          <t>Epic 7 progress: 40 of 149 items Done  (26.8%)</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L148"/>
+  <dimension ref="A1:L150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10113,6 +10113,118 @@
         </is>
       </c>
     </row>
+    <row r="149" ht="70" customHeight="1">
+      <c r="A149" s="16" t="inlineStr">
+        <is>
+          <t>U7-02.1</t>
+        </is>
+      </c>
+      <c r="B149" s="16" t="inlineStr">
+        <is>
+          <t>Desk.js</t>
+        </is>
+      </c>
+      <c r="C149" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D149" s="15" t="inlineStr">
+        <is>
+          <t>Copy + IA</t>
+        </is>
+      </c>
+      <c r="E149" s="16" t="inlineStr">
+        <is>
+          <t>On-Fire CTA -- split Chase (theirs) vs Respond (mine)</t>
+        </is>
+      </c>
+      <c r="F149" s="16" t="inlineStr">
+        <is>
+          <t>Founder wireframe (2026-08-17): the On-Fire list carries two very different asks -- "I owe someone a reply" vs "someone owes me". Both landed as CTA "chase" from the backend, so both said "Chase". Rewired the label client-side by comparing target_owner_id to the current user id -- when I own the target, "chase" reads and behaves as "Respond" (dark button, routes into MyWork with the task focused for reply). No backend change.</t>
+        </is>
+      </c>
+      <c r="G149" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H149" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I149" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J149" s="16" t="n"/>
+      <c r="K149" s="16" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17. Verified on Sharma tenant: 12 on-fire items assigned to other users still read Chase; the Respond path is exercised once a task lands on the viewer.</t>
+        </is>
+      </c>
+      <c r="L149" s="16" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17 (Lovable wireframe)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="70" customHeight="1">
+      <c r="A150" s="16" t="inlineStr">
+        <is>
+          <t>U7-02.2</t>
+        </is>
+      </c>
+      <c r="B150" s="16" t="inlineStr">
+        <is>
+          <t>DecisionDialog.js, Desk.js</t>
+        </is>
+      </c>
+      <c r="C150" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D150" s="15" t="inlineStr">
+        <is>
+          <t>Visual + Interaction</t>
+        </is>
+      </c>
+      <c r="E150" s="16" t="inlineStr">
+        <is>
+          <t>Decision Dialog rebuilt per approval wireframe</t>
+        </is>
+      </c>
+      <c r="F150" s="16" t="inlineStr">
+        <is>
+          <t>Founder wireframe (2026-08-17): the Decision Dialog was a comment stream with approve/reject buried elsewhere; the mock shows one sheet that answers "what am I deciding, what does it unblock, yes/no, who does what next, note back to the raiser". Full rewrite: (1) header = title + amount (heuristic parse from items[].detail) + "Part of &lt;workflow&gt;" chip, (2) unblocks callout when there are still-blocked spawned tasks, (3) big APPROVE + REJECT (reject is two-step because it cascade-deletes spawned work), (4) "What happens next" timeline -- Raised by / Waiting on your decision / spawned tasks with "Goes to &lt;name&gt;", (5) "Send a note" collapsible using the existing /decisions/:id/comment endpoint plus a placeholder voice mic. Also fixed the deep-link bug where /inbox?decision=&lt;id&gt; would silently no-op if the decision was already resolved (no matching desk card).</t>
+        </is>
+      </c>
+      <c r="G150" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H150" s="16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I150" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J150" s="16" t="n"/>
+      <c r="K150" s="16" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17. Verified via /inbox?decision=&lt;pending-approval decision id&gt;: dialog renders title / summary / Unblocks 1 task / APPROVE + REJECT / What happens next timeline (Raised by, Waiting on your decision, spawned task with Goes to &lt;assignee&gt;) / Send a note section with mic + textarea + SEND NOTE. All hooks wire to /api/decisions/{id}/approve and /api/decisions/{id}/reject which already exist.</t>
+        </is>
+      </c>
+      <c r="L150" s="16" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17 (Lovable wireframe)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
@@ -1472,7 +1472,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 7 progress: 40 of 149 items Done  (26.8%)</t>
+          <t>Epic 7 progress: 41 of 150 items Done  (27.3%)</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L150"/>
+  <dimension ref="A1:L151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10225,6 +10225,62 @@
         </is>
       </c>
     </row>
+    <row r="151" ht="70" customHeight="1">
+      <c r="A151" s="16" t="inlineStr">
+        <is>
+          <t>U7-02.3</t>
+        </is>
+      </c>
+      <c r="B151" s="16" t="inlineStr">
+        <is>
+          <t>backend/routers/desk.py</t>
+        </is>
+      </c>
+      <c r="C151" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D151" s="15" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="E151" s="16" t="inlineStr">
+        <is>
+          <t>Needs Your Decision chip -- count Dex-created decisions</t>
+        </is>
+      </c>
+      <c r="F151" s="16" t="inlineStr">
+        <is>
+          <t>Traced end-to-end while answering the founder question "from Dex, owner will raise the decision -- where will the decision come?". Two bugs in the desk query, one behavior: (a) status filter used `"pending"` but process_voice_note writes `"pending_approval"`, (b) approver_id fallback used `{"$in":[None,""]}` which does not match documents where the field is absent -- and Dex-created decisions do not set the field at all. Both bugs together meant the chip counted 0 for every tenant whose decisions came through the voice/text capture path (i.e., every real tenant). Widened the query in both _cards_needs_decision and _pending_decisions_for (desk summary counter) to accept both status spellings AND treat missing/null/empty approver_id as unassigned.</t>
+        </is>
+      </c>
+      <c r="G151" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H151" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I151" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J151" s="16" t="n"/>
+      <c r="K151" s="16" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17. Verified end-to-end on Sharma tenant: (1) existing "Hire a dispatch coordinator" decision (previously 0) now counts as 1, (2) fresh decision created via /api/voice-notes/text ("Approve Rescheduling of Acme Packaging Payment", Rs 4,80,000, 2 spawned tasks) surfaces on the chip within ~4s and opens in the new DecisionDialog with amount parsed, timeline populated (Priya Nair, Amit Verma as spawned assignees), and approve/reject wired. Renaming to a single canonical status left for a later sweep -- the widened filter fixes the visible bug now.</t>
+        </is>
+      </c>
+      <c r="L151" s="16" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
@@ -1472,7 +1472,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 7 progress: 41 of 150 items Done  (27.3%)</t>
+          <t>Epic 7 progress: 44 of 153 items Done  (28.8%)</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L151"/>
+  <dimension ref="A1:L154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10281,6 +10281,174 @@
         </is>
       </c>
     </row>
+    <row r="152" ht="70" customHeight="1">
+      <c r="A152" s="16" t="inlineStr">
+        <is>
+          <t>RD-1.1</t>
+        </is>
+      </c>
+      <c r="B152" s="16" t="inlineStr">
+        <is>
+          <t>index.css, tailwind.config.js</t>
+        </is>
+      </c>
+      <c r="C152" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D152" s="15" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="E152" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1a -- retune tokens to the reference design language</t>
+        </is>
+      </c>
+      <c r="F152" s="16" t="inlineStr">
+        <is>
+          <t>Founder ask: delete the "OS" theme entirely and rebuild against the 20 reference mockups in DecisionOS/UI REfrence, keeping only the logo and the brand indigo. Colour rule agreed up front: indigo replaces black on ACTION surfaces only (buttons, active nav, toggles, focus ring) -- text, headings and borders stay neutral, because the reference uses black for both jobs and a literal substitution turns body copy indigo. Token work: neutral ramp moved off the blue-tinted 210-228 hues onto 240 (the brand family) at 4-12% saturation; hairlines lightened; page ground switched from neutral-50 to pure white so canvas and cards share one surface and the hairline is the only separator; --shadow-xs/sm set to none (resting surfaces are flat, shadow survives only for genuinely floating things); Instrument Serif added as the display face; .label-mono stripped of its mono face + uppercase + 0.12em tracking (that single class is what made every screen read as a terminal); ambient canvas glow + dot-grid removed.</t>
+        </is>
+      </c>
+      <c r="G152" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H152" s="16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I152" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J152" s="16" t="n"/>
+      <c r="K152" s="16" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17 on branch redesign-midday. Verified via computed styles: --background 0 0% 100%, --hairline 240 11% 92%, --shadow-sm none, label-mono now Inter/normal-case/normal-tracking. Instrument Serif loads and renders distinctly (345px vs 488px for the same 48px string).</t>
+        </is>
+      </c>
+      <c r="L152" s="16" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17 (UI REfrence folder)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="70" customHeight="1">
+      <c r="A153" s="16" t="inlineStr">
+        <is>
+          <t>RD-1.2</t>
+        </is>
+      </c>
+      <c r="B153" s="16" t="inlineStr">
+        <is>
+          <t>Layout.js</t>
+        </is>
+      </c>
+      <c r="C153" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D153" s="15" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="E153" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1b -- app shell becomes icon rail + full-width top bar</t>
+        </is>
+      </c>
+      <c r="F153" s="16" t="inlineStr">
+        <is>
+          <t>Reference shell is a 58px icon-only rail plus a top bar carrying one global search. Replaced the 256px labelled sidebar: nav labels moved to hover tooltips (kept in the DOM with aria-label so screen readers and keyboard users are unaffected), and tenant name + user identity + sign-out moved into an avatar popover at the rail foot. The "Signed in as &lt;name&gt; [ROLE]" block in the old top bar was decoration on every screen and is gone. Search submits to Dex (/brain?q=), the app's real ask-anything surface, so the field does actual work rather than being a decorative stub.</t>
+        </is>
+      </c>
+      <c r="G153" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H153" s="16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I153" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J153" s="16" t="n"/>
+      <c r="K153" s="16" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17. DEVIATION FROM REFERENCE, deliberate: the reference puts its mark in the rail's top cell, which requires an icon mark. Our artwork has none -- the supplied lockup is horizontal and renders 108px wide at its smallest legible size, which overflowed the 58px rail by ~51px (measured). Wordmark.jsx is explicit that a redrawn approximation is a different logo, so rather than invent a glyph the top bar spans the full width and carries the lockup at its left, pixel-exact; the rail starts below it. Revisit if an icon-only brand asset is ever supplied. Verified: header 1400x64 at y=0, logo ends x=128 (no clip), rail 58px at y=64, main starts x=58, no horizontal overflow, 8 nav icons, tooltips opacity-0 + pointer-events-none.</t>
+        </is>
+      </c>
+      <c r="L153" s="16" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17 (UI REfrence folder)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="70" customHeight="1">
+      <c r="A154" s="16" t="inlineStr">
+        <is>
+          <t>RD-1.3</t>
+        </is>
+      </c>
+      <c r="B154" s="16" t="inlineStr">
+        <is>
+          <t>common.js, ui/button.jsx, ui/card.jsx</t>
+        </is>
+      </c>
+      <c r="C154" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D154" s="15" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="E154" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1c -- shared primitives restyled flat</t>
+        </is>
+      </c>
+      <c r="F154" s="16" t="inlineStr">
+        <is>
+          <t>Chip rebuilt: was solid saturated fills (yellow/blue/black) with a hard border, uppercase and wide tracking -- ten rows meant ten shouting blocks. Now a tint-bg + darker-text pair off the semantic ramp, no border, capitalized. Deliberately no indigo default: indigo is the action colour and a status pill is not an action, so neutral states are grey. EmptyState lost its dashed box (read as a drop-zone, wrong affordance) for centred quiet prose with the CTA as the only coloured element. Skeletons moved from bg-black/10 + rounded-none to bg-muted + rounded. Button variants lost every drop shadow; default fills with indigo. Card lost its shadow to match .card-brutal.</t>
+        </is>
+      </c>
+      <c r="G154" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H154" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I154" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J154" s="16" t="n"/>
+      <c r="K154" s="16" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17. Verified live: 20 chips on MyWork render tinted (caution-50 bg rgb(255,251,235) / caution-800 text rgb(145,64,13)), border-width 0, text-transform capitalize. All 10 desktop pages render with no horizontal overflow.</t>
+        </is>
+      </c>
+      <c r="L154" s="16" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17 (UI REfrence folder)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
@@ -1472,7 +1472,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 7 progress: 44 of 153 items Done  (28.8%)</t>
+          <t>Epic 7 progress: 46 of 155 items Done  (29.7%)</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L154"/>
+  <dimension ref="A1:L156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10449,6 +10449,118 @@
         </is>
       </c>
     </row>
+    <row r="155" ht="70" customHeight="1">
+      <c r="A155" s="16" t="inlineStr">
+        <is>
+          <t>RD-2.1</t>
+        </is>
+      </c>
+      <c r="B155" s="16" t="inlineStr">
+        <is>
+          <t>Desk.js</t>
+        </is>
+      </c>
+      <c r="C155" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D155" s="15" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="E155" s="16" t="inlineStr">
+        <is>
+          <t>Phase 2a -- Decision Desk rebuilt on the reference language</t>
+        </is>
+      </c>
+      <c r="F155" s="16" t="inlineStr">
+        <is>
+          <t>Greeting promoted to the page's editorial moment: 36px Instrument Serif, split on the last comma so the salutation carries full ink and the name goes muted (the reference's two-weight greeting). Was 24px Inter at font-black/tracking-tighter, which read as a shouted label. Dex narrative lost its hard border, brutal shadow and solid dark avatar tile for a quiet indigo-tinted sparkle plus prose. Trends and Shortcuts became hairline cards with sentence-case captions. Chip strip went from bordered uppercase blocks that inverted to solid dark, to borderless pills with an indigo tint on the active one. Desk cards are hairline rows: context line drops the mono face (it is prose, not data) while the amount keeps mono + tabular-nums (it is data and must align). CTA arrow dropped; only Review/Respond -- the actions genuinely ON the viewer -- take the indigo fill, while Chase/Nudge sit a level quieter as hairline buttons. Empty state lost its dashed drop-zone box.</t>
+        </is>
+      </c>
+      <c r="G155" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H155" s="16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I155" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J155" s="16" t="n"/>
+      <c r="K155" s="16" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17. Verified in-browser: serif greeting renders with the muted name, flat cards, pill chips with indigo-tint active state, indigo Review CTA.</t>
+        </is>
+      </c>
+      <c r="L155" s="16" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17 (UI REfrence folder)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="70" customHeight="1">
+      <c r="A156" s="16" t="inlineStr">
+        <is>
+          <t>RD-2.2</t>
+        </is>
+      </c>
+      <c r="B156" s="16" t="inlineStr">
+        <is>
+          <t>MyWork.js</t>
+        </is>
+      </c>
+      <c r="C156" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D156" s="15" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="E156" s="16" t="inlineStr">
+        <is>
+          <t>Phase 2b -- MyWork rebuilt on the reference language</t>
+        </is>
+      </c>
+      <c r="F156" s="16" t="inlineStr">
+        <is>
+          <t>Entered with 81 border-black, 41 uppercase-tracking and two competing action colours. The CTRL const (every toolbar button) moved from uppercase + wide tracking + hard black border to a hairline sentence-case pill, which fixed the whole toolbar in one line. Active states across scope toggles, view toggles and AI Priority collapsed onto one indigo tint -- AI Priority in particular was solid brand-yellow at REST, making the loudest thing on the page a control the user had not touched. Category tabs match the Desk chip strip. bg-brand-ink (the brutalist near-black primary) and bg-brand-blue (a second action colour) both collapse onto --primary, so the palette now has exactly one action colour. Status labels moved to sentence case with quiet tints; Overdue deliberately keeps its solid red because it is a real alarm. Brand-yellow hover states became neutral accent.</t>
+        </is>
+      </c>
+      <c r="G156" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H156" s="16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I156" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J156" s="16" t="n"/>
+      <c r="K156" s="16" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17. End state: 0 border-black, 0 bg-brand-ink, 0 bg-brand-blue, 0 shadow-brutal, 2 uppercase-tracking left (both in non-visible branches). Verified in-browser: Complete button computes rgb(55,58,205) = brand indigo (was rgb(10,10,11) near-black); expanded task card internals render; all 10 desktop surfaces OK with no horizontal overflow.</t>
+        </is>
+      </c>
+      <c r="L156" s="16" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17 (UI REfrence folder)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
@@ -1472,7 +1472,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 7 progress: 46 of 155 items Done  (29.7%)</t>
+          <t>Epic 7 progress: 48 of 157 items Done  (30.6%)</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L156"/>
+  <dimension ref="A1:L158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10561,6 +10561,118 @@
         </is>
       </c>
     </row>
+    <row r="157" ht="70" customHeight="1">
+      <c r="A157" s="16" t="inlineStr">
+        <is>
+          <t>RD-3.1</t>
+        </is>
+      </c>
+      <c r="B157" s="16" t="inlineStr">
+        <is>
+          <t>CRM.js</t>
+        </is>
+      </c>
+      <c r="C157" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D157" s="15" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="E157" s="16" t="inlineStr">
+        <is>
+          <t>Phase 3a -- CRM list rebuilt on the reference language</t>
+        </is>
+      </c>
+      <c r="F157" s="16" t="inlineStr">
+        <is>
+          <t>Lifecycle stage chips were five different colour systems across two arrays (black/10, black/30-on-white, brand-blue/20, brand-green/20, solid brand-yellow); re-tinted onto the semantic ramp so colour tracks meaning. Underline tab strip keeps its structure -- correct control for two exclusive lanes -- but loses uppercase/wide tracking and the solid dark count slab; underline moves to indigo. Search/status/sort become hairline rounded controls. Contact card goes hairline with a border-darkening hover, type chip becomes a tint pill, key signal drops font-mono+semibold for medium + tabular-nums. Form inputs lose the mono face (mono in a text field made every form read as a config file). Dialog titles take the serif display face.</t>
+        </is>
+      </c>
+      <c r="G157" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H157" s="16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I157" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J157" s="16" t="n"/>
+      <c r="K157" s="16" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17. TWO REAL BUGS FOUND while re-tinting, both invisible until now: (1) `bg-brand-green/20 text-brand-green` on the "Active" lifecycle chip -- brand-green is defined nowhere in tailwind.config.js or index.css, so that chip had been rendering with no background at all; (2) the type chip called .toUpperCase() on the DATA, so it stayed shouting after the stylesheet went sentence case. Also fixed a layout bug: the contact card is a &lt;button&gt;, which centres its content, so any card missing the optional key-signal line had its title sitting 16px below its neighbours in a stretched grid row. Card is now flex-col with an mt-auto footer -- verified titles AND footers now align at identical y across the row (299/299/299 and 370/370/370, was 299/315/299). End state: 0 border-black, 0 shadow-brutal, 0 brand-ink, 0 uppercase.</t>
+        </is>
+      </c>
+      <c r="L157" s="16" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17 (UI REfrence folder)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="70" customHeight="1">
+      <c r="A158" s="16" t="inlineStr">
+        <is>
+          <t>RD-3.2</t>
+        </is>
+      </c>
+      <c r="B158" s="16" t="inlineStr">
+        <is>
+          <t>ContactProfile.js</t>
+        </is>
+      </c>
+      <c r="C158" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D158" s="15" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="E158" s="16" t="inlineStr">
+        <is>
+          <t>Phase 3b -- ContactProfile rebuilt on the reference language</t>
+        </is>
+      </c>
+      <c r="F158" s="16" t="inlineStr">
+        <is>
+          <t>Stat tiles move from font-black/tracking-tight (a row of them read as a scoreboard) to a small muted caption over a large medium-weight tabular number. Section headings drop uppercase/extrabold for a plain medium line with the count in a quiet pill instead of parentheses. The Table header was a solid dark bar with mono caps -- it read as a terminal -- and is now muted grey header text on the card ground with one hairline beneath. ScoreBox loses its 2px black square for a soft tinted tile. Page title takes the serif display face. Activity-kind and payment-direction chips move onto semantic tints (payment in = success, out = neutral).</t>
+        </is>
+      </c>
+      <c r="G158" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H158" s="16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I158" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J158" s="16" t="n"/>
+      <c r="K158" s="16" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17. Self-corrected during the pass: the bulk brand-yellow sweep caught the "Analyze this relationship with AI" banner and landed it on a caution tint -- that banner is an OFFER, not a warning, and a yellow plate told the user something was wrong when nothing was. Reverted to a neutral hairline card; the DexBadge already supplies its only accent. End state: 0 border-black, 0 shadow-brutal, 0 brand-yellow, 0 brand-ink, 0 uppercase-tracking. All 8 desktop surfaces verified with no horizontal overflow.</t>
+        </is>
+      </c>
+      <c r="L158" s="16" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17 (UI REfrence folder)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
@@ -1472,7 +1472,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 7 progress: 48 of 157 items Done  (30.6%)</t>
+          <t>Epic 7 progress: 49 of 158 items Done  (31.0%)</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L158"/>
+  <dimension ref="A1:L159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10673,6 +10673,62 @@
         </is>
       </c>
     </row>
+    <row r="159" ht="70" customHeight="1">
+      <c r="A159" s="16" t="inlineStr">
+        <is>
+          <t>RD-4.1</t>
+        </is>
+      </c>
+      <c r="B159" s="16" t="inlineStr">
+        <is>
+          <t>Ledger.js, finance/ReviewPanel.js, finance/WhatsAppCard.js, Captures.js</t>
+        </is>
+      </c>
+      <c r="C159" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D159" s="15" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="E159" s="16" t="inlineStr">
+        <is>
+          <t>Phase 4 -- Finance rebuilt on the reference language</t>
+        </is>
+      </c>
+      <c r="F159" s="16" t="inlineStr">
+        <is>
+          <t>Biggest surface in the app (Ledger alone is ~1100 lines) and the one the reference speaks to most directly, since its strongest pattern is the data table. Six tabs were a welded segmented block of uppercase slabs whose active state inverted to solid dark -- the loudest element on a page whose job is showing money; now the same pill strip Desk and MyWork use. Table headers move from mono caps to muted grey text over a single hairline, and rows gain a quiet hover. KPI tiles drop font-black/tracking-tight for a muted caption over a large medium-weight tabular number, matching ContactProfile Stat. Status chips go semantic: paid/received = success tint, awaiting/unpaid = caution tint (was solid brand-yellow). SOURCE_CHIP / LEVEL_DOT / LEVEL_ACCENT maps re-tinted off raw legacy tokens (bg-green-600, brand-blue, brand-yellow) onto the semantic ramp -- WhatsApp keeps a green tint because it is a real brand mark. Dialog titles take the serif display face. Capture hero upload tiles become hairline rounded buttons.</t>
+        </is>
+      </c>
+      <c r="G159" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H159" s="16" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I159" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J159" s="16" t="n"/>
+      <c r="K159" s="16" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17. The U7-08.1 invoice work (overdue callout, status filter chips, sort, filtered subtotal) survives intact and now renders in the new language -- overdue keeps its solid red because it is a real alarm. End state across all four files: 0 border-black, 0 shadow-brutal, 0 uppercase-tracking, 0 brand-yellow, 0 brand-ink. Verified in-browser: all SIX finance tabs (overview/revenue/expenses/assets/inventory/inbox) render, plus all 9 desktop pages, with no horizontal overflow.</t>
+        </is>
+      </c>
+      <c r="L159" s="16" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17 (UI REfrence folder)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
@@ -1472,7 +1472,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 7 progress: 49 of 158 items Done  (31.0%)</t>
+          <t>Epic 7 progress: 50 of 160 items Done  (31.2%)</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L159"/>
+  <dimension ref="A1:L161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10729,6 +10729,118 @@
         </is>
       </c>
     </row>
+    <row r="160" ht="70" customHeight="1">
+      <c r="A160" s="16" t="inlineStr">
+        <is>
+          <t>RD-5.1</t>
+        </is>
+      </c>
+      <c r="B160" s="16" t="inlineStr">
+        <is>
+          <t>Team, Ops, Dex, Workflows, Leave, Settings, Calendar, Journal, Coach, People, Contacts, Notifications, Login, Signup, Landing, onboarding/*, 13 components</t>
+        </is>
+      </c>
+      <c r="C160" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D160" s="15" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="E160" s="16" t="inlineStr">
+        <is>
+          <t>Phase 5 -- the long tail of desktop surfaces</t>
+        </is>
+      </c>
+      <c r="F160" s="16" t="inlineStr">
+        <is>
+          <t>Applied the vocabulary settled in P1-P4 across every remaining desktop surface: 34 pages + components, plus the 5-file onboarding flow reached through Signup. Same rules throughout -- border-black to hairline, one indigo action colour, sentence case, no resting shadow, semantic tints for status. Large uppercase headings become the serif display face; smaller ones drop to medium-weight sentence case.</t>
+        </is>
+      </c>
+      <c r="G160" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H160" s="16" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I160" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J160" s="16" t="n"/>
+      <c r="K160" s="16" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-17. PROCESS NOTE worth keeping: the first sweep script was reverted before commit because it did two things wrong. (1) A trailing `.replace('   ', ' ')` intended to tidy leftover double spaces collapsed SOURCE INDENTATION across all 34 files. (2) Rules ran over whole files, so they rewrote text inside COMMENTS -- producing comments that asserted the opposite of the truth (a note explaining the old brutalist bar was rewritten to describe the new one). Reverted via git checkout (all prior phases were already committed, so nothing was lost) and redone in three safer passes: v2 confined edits to string literals inside className expressions; v3 went line-by-line skipping comment lines, to reach bare consts and template literals with ${} that the regex could not parse; v4 handled uppercase headings, which paired `uppercase` with tracking-TIGHT rather than tracking-wider and had sailed through every earlier pass -- that gap was leaving whole narrative paragraphs shouting in caps on Operating Score and the Landing hero. Verified after each pass that indentation matched HEAD exactly and that zero comment lines had changed. End state: 0 brutalist tokens on any code line across pages + components. All 16 desktop surfaces render with no horizontal overflow; onboarding verified visually.</t>
+        </is>
+      </c>
+      <c r="L160" s="16" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17 (UI REfrence folder)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="70" customHeight="1">
+      <c r="A161" s="16" t="inlineStr">
+        <is>
+          <t>RD-5.2</t>
+        </is>
+      </c>
+      <c r="B161" s="16" t="inlineStr">
+        <is>
+          <t>pages/admin/*</t>
+        </is>
+      </c>
+      <c r="C161" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D161" s="15" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="E161" s="16" t="inlineStr">
+        <is>
+          <t>Admin portal deliberately left on the old theme</t>
+        </is>
+      </c>
+      <c r="F161" s="16" t="inlineStr">
+        <is>
+          <t>pages/admin/AdminLogin.js, AdminPortal.js and AdminSections.js still carry the retired brutalist styling. Left alone on purpose: the admin portal is the internal super-admin surface, not part of the tenant-facing product, and it has a different audience and no reference mockups. Flagging it so the inconsistency is a recorded decision rather than an oversight.</t>
+        </is>
+      </c>
+      <c r="G161" s="16" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H161" s="16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I161" s="19" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J161" s="16" t="n"/>
+      <c r="K161" s="16" t="inlineStr">
+        <is>
+          <t>Noted 2026-08-17 during the RD-5 sweep.</t>
+        </is>
+      </c>
+      <c r="L161" s="16" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-17 (UI REfrence folder)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
@@ -1472,7 +1472,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 7 progress: 50 of 160 items Done  (31.2%)</t>
+          <t>Epic 7 progress: 52 of 162 items Done  (32.1%)</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L161"/>
+  <dimension ref="A1:L163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10841,6 +10841,118 @@
         </is>
       </c>
     </row>
+    <row r="162" ht="70" customHeight="1">
+      <c r="A162" s="16" t="inlineStr">
+        <is>
+          <t>RD-6</t>
+        </is>
+      </c>
+      <c r="B162" s="16" t="inlineStr">
+        <is>
+          <t>tailwind.config.js, index.css, Layout.js, 22 pages/components</t>
+        </is>
+      </c>
+      <c r="C162" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D162" s="15" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="E162" s="16" t="inlineStr">
+        <is>
+          <t>Readability + density pass -- type scale, sidebar, whitespace</t>
+        </is>
+      </c>
+      <c r="F162" s="16" t="inlineStr">
+        <is>
+          <t>Founder: "its not readable, side bar is small, fonts are small ... there is lot of white space there also ... give me the premium look." Measured before touching anything: 424 text-sm (14px) + 322 text-xs (12px) call sites against only 36 text-base -- almost every word in the app was 12-14px. Fixed via one Tailwind fontSize override (xs 12-&gt;13, sm 14-&gt;15, lg 18-&gt;19, xl 20-&gt;22, 2xl 24-&gt;27, 3xl 30-&gt;34, 4xl 36-&gt;42) so all 746 call sites lifted without per-site edits, plus killed 104 hardcoded text-[9/10/11px] literals that bypassed the scale. Sidebar: the 58px icon-only rail from RD-1 (names visible only on hover) replaced with a 240px labelled sidebar -- always-visible 15px labels, 40px rows, the wordmark restored to its top-left cell, user block showing name + workspace. Whitespace: py-20/16 -&gt; py-12, mb-10/8 -&gt; mb-6, mt-8 -&gt; mt-6, gap-8 -&gt; gap-6, p-12/10 -&gt; p-8 across 22 files.</t>
+        </is>
+      </c>
+      <c r="G162" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H162" s="16" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I162" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J162" s="16" t="n"/>
+      <c r="K162" s="16" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-18 (commit 2b6ab57). TWO BUGS found and fixed, both making desktop render SMALLER type than mobile: (1) .label-mono had competing definitions -- @apply text-xs but a later rule set font-size: var(--text-label), which was 11px on desktop / 13px on mobile, so every eyebrow painted at 11px regardless of the utility; (2) the Recharts font-size override lived inside the mobile-only media query, so every chart axis was 11px on desktop / 13px on mobile. Also consolidated a second competing accent (brand-blue #002FA7 sitting beside the indigo primary #373ACD) onto the semantic ramp across 37 call sites, and fixed ACTIVITY_META in ContactProfile which had escaped every earlier sweep and still carried bg-brand-green -- the same phantom undefined token found on the CRM lifecycle chip. Verified by measuring the painted font-size of every leaf text node on 9 screens: zero sub-13px text anywhere.</t>
+        </is>
+      </c>
+      <c r="L162" s="16" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="70" customHeight="1">
+      <c r="A163" s="16" t="inlineStr">
+        <is>
+          <t>RD-6.1</t>
+        </is>
+      </c>
+      <c r="B163" s="16" t="inlineStr">
+        <is>
+          <t>Desk.js</t>
+        </is>
+      </c>
+      <c r="C163" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D163" s="15" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="E163" s="16" t="inlineStr">
+        <is>
+          <t>Widen Desk content column; fix a JSX comment bug</t>
+        </is>
+      </c>
+      <c r="F163" s="16" t="inlineStr">
+        <is>
+          <t>Desk was capped at max-w-5xl (1024px). With the 240px sidebar already taking width that left ~90px dead either side at 1440px and ~330px at 1920px -- part of the "lot of white space" complaint. Widened to max-w-6xl (1136px).</t>
+        </is>
+      </c>
+      <c r="G163" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H163" s="16" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I163" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J163" s="16" t="n"/>
+      <c r="K163" s="16" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-18 (commit f8523ba). Self-caught process bug: the first attempt wrote the explanatory comment as {{/* ... */}} directly inside return (, making it a sibling of the root element -- invalid JSX. The dev server kept serving the previous bundle, so the change looked like a no-op (DOM still reported max-w-5xl while the file on disk said 6xl). Fixed by moving the comment above the return as a plain // comment, then audited the rest of the session for the same pattern and parse-checked the entire tree through @babel/preset-react -- 155 files, all clean. Verified live: every screen now uses ~95% of its content column width.</t>
+        </is>
+      </c>
+      <c r="L163" s="16" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
@@ -1443,7 +1443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1472,7 +1472,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 7 progress: 50 of 160 items Done  (31.2%)</t>
+          <t>Epic 7 progress: 64 of 153 in-scope items Done  (42%).  7 items dropped as obsolete after the karma redesign; validated screen-by-screen vs the new UI on 2026-08-20.</t>
         </is>
       </c>
     </row>
@@ -1525,14 +1525,14 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
@@ -1558,19 +1558,19 @@
         </is>
       </c>
       <c r="C7" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="F7" s="15" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="G7" s="16" t="inlineStr">
@@ -1591,19 +1591,19 @@
         </is>
       </c>
       <c r="C8" s="17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D8" s="17" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="G8" s="18" t="inlineStr">
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
@@ -1690,19 +1690,19 @@
         </is>
       </c>
       <c r="C11" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="G11" s="16" t="inlineStr">
@@ -1723,19 +1723,19 @@
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="G12" s="18" t="inlineStr">
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
@@ -1822,19 +1822,19 @@
         </is>
       </c>
       <c r="C15" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="F15" s="15" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
@@ -2020,19 +2020,19 @@
         </is>
       </c>
       <c r="C21" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D21" s="15" t="n">
         <v>6</v>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="F21" s="15" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="G21" s="16" t="inlineStr">
@@ -2053,19 +2053,19 @@
         </is>
       </c>
       <c r="C22" s="17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D22" s="17" t="n">
         <v>5</v>
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="G22" s="18" t="inlineStr">
@@ -2104,6 +2104,39 @@
       <c r="G23" s="16" t="inlineStr">
         <is>
           <t>UX copy sweep (buttons, empty states, errors, tooltips). Final E2E golden path across desktop + mobile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Redesign log</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>KR/RD redesign changelog (shipped during rebuild)</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>21</v>
+      </c>
+      <c r="D24" t="n">
+        <v>22</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Items logged during the karma/KR redesign + RD token retune; filed under Sprint 7 in the backlog. Mostly already shipped.</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2331,11 @@
         </is>
       </c>
       <c r="J3" s="13" t="inlineStr"/>
-      <c r="K3" s="13" t="inlineStr"/>
+      <c r="K3" s="13" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Score numeral counts up (CountUp, reduced-motion guarded); ArcGauge ring fill doesn't animate from 0 on mount.</t>
+        </is>
+      </c>
       <c r="L3" s="13" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -2854,7 +2891,11 @@
         </is>
       </c>
       <c r="J13" s="13" t="inlineStr"/>
-      <c r="K13" s="13" t="inlineStr"/>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: No hover WorkCoach mini-card on leaderboard rows.</t>
+        </is>
+      </c>
       <c r="L13" s="13" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -3182,11 +3223,15 @@
       </c>
       <c r="I19" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J19" s="13" t="inlineStr"/>
-      <c r="K19" s="13" t="inlineStr"/>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] DONE: Page rewritten on karma semantic tokens; 0 pre-rebrand hardcoded colors (OperatingScore.js).</t>
+        </is>
+      </c>
       <c r="L19" s="13" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -3234,11 +3279,15 @@
       </c>
       <c r="I20" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J20" s="13" t="inlineStr"/>
-      <c r="K20" s="13" t="inlineStr"/>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] DONE: Adopted DS type ramp font-display + text-h2/h3; only intended font-mono numerals remain.</t>
+        </is>
+      </c>
       <c r="L20" s="13" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -3346,7 +3395,11 @@
         </is>
       </c>
       <c r="J22" s="13" t="inlineStr"/>
-      <c r="K22" s="13" t="inlineStr"/>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: ScoreMeter role=progressbar + values added; per-category descriptive aria-label + overall progressbar still missing.</t>
+        </is>
+      </c>
       <c r="L22" s="13" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -3398,7 +3451,11 @@
         </is>
       </c>
       <c r="J23" s="13" t="inlineStr"/>
-      <c r="K23" s="13" t="inlineStr"/>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: No OperatingScoreMobile / responsive mobile pass (also U7-17.1).</t>
+        </is>
+      </c>
       <c r="L23" s="13" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -3446,11 +3503,15 @@
       </c>
       <c r="I24" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="J24" s="13" t="inlineStr"/>
-      <c r="K24" s="13" t="inlineStr"/>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] DROP: Superseded by Phase A: owner-only gate removed, non-owners get real SelfView, nav shown to all; 403 gone (server.py:2892).</t>
+        </is>
+      </c>
       <c r="L24" s="13" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -3502,7 +3563,11 @@
         </is>
       </c>
       <c r="J25" s="13" t="inlineStr"/>
-      <c r="K25" s="13" t="inlineStr"/>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: Weekly ops-score email opt-in toggle + template not built (frontend of U7-01.38).</t>
+        </is>
+      </c>
       <c r="L25" s="13" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -3554,7 +3619,11 @@
         </is>
       </c>
       <c r="J26" s="13" t="inlineStr"/>
-      <c r="K26" s="13" t="inlineStr"/>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: Shareable one-pager token link + generator not built (frontend of U7-01.39).</t>
+        </is>
+      </c>
       <c r="L26" s="13" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -3602,11 +3671,15 @@
       </c>
       <c r="I27" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J27" s="16" t="inlineStr"/>
-      <c r="K27" s="16" t="inlineStr"/>
+      <c r="K27" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] DONE: Landing hero one-liner 'Speak the decision. We run the company.' + indigo accent (Landing.js:50-57).</t>
+        </is>
+      </c>
       <c r="L27" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -3658,7 +3731,11 @@
         </is>
       </c>
       <c r="J28" s="18" t="inlineStr"/>
-      <c r="K28" s="18" t="inlineStr"/>
+      <c r="K28" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: Login errors are raw backend detail passthrough; no actionable copy/'Reset it?' link.</t>
+        </is>
+      </c>
       <c r="L28" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -3706,11 +3783,15 @@
       </c>
       <c r="I29" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="J29" s="16" t="inlineStr"/>
-      <c r="K29" s="16" t="inlineStr"/>
+      <c r="K29" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] DROP: Obsolete: two-step company+role signup wizard removed; roles now AI-generated from interview (Signup.js PHASES).</t>
+        </is>
+      </c>
       <c r="L29" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -3758,11 +3839,15 @@
       </c>
       <c r="I30" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J30" s="18" t="inlineStr"/>
-      <c r="K30" s="18" t="inlineStr"/>
+      <c r="K30" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] DONE: Focus rings via --focus-ring both themes; form tab order Email-&gt;Password-&gt;Submit; Enter submits (Login.js:228, index.css:520).</t>
+        </is>
+      </c>
       <c r="L30" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -3814,7 +3899,11 @@
         </is>
       </c>
       <c r="J31" s="16" t="inlineStr"/>
-      <c r="K31" s="16" t="inlineStr"/>
+      <c r="K31" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Indigo accent/CTA adopted, but hardcoded neutrals (#16161a/#f7f5f2) + font-black type ramp remain on Landing.</t>
+        </is>
+      </c>
       <c r="L31" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -3866,7 +3955,11 @@
         </is>
       </c>
       <c r="J32" s="18" t="inlineStr"/>
-      <c r="K32" s="18" t="inlineStr"/>
+      <c r="K32" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: No bottom-anchored/sticky primary CTA + no iOS safe-area handling on auth.</t>
+        </is>
+      </c>
       <c r="L32" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -3914,11 +4007,15 @@
       </c>
       <c r="I33" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J33" s="16" t="inlineStr"/>
-      <c r="K33" s="16" t="inlineStr"/>
+      <c r="K33" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] DONE: Persistent 4-phase progress bar (signup-phase-bar, Signup.js:54-61).</t>
+        </is>
+      </c>
       <c r="L33" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -3966,11 +4063,15 @@
       </c>
       <c r="I34" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J34" s="18" t="inlineStr"/>
-      <c r="K34" s="18" t="inlineStr"/>
+      <c r="K34" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] DONE: WebsiteIntel rotating step captions + scanner, no spinner-in-void (WebsiteIntel.js:8-14).</t>
+        </is>
+      </c>
       <c r="L34" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -4022,7 +4123,11 @@
         </is>
       </c>
       <c r="J35" s="16" t="inlineStr"/>
-      <c r="K35" s="16" t="inlineStr"/>
+      <c r="K35" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Conversational one-answer-per-turn frame shipped; actual question wording is backend-generated (VoiceInterview).</t>
+        </is>
+      </c>
       <c r="L35" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -4070,11 +4175,15 @@
       </c>
       <c r="I36" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J36" s="18" t="inlineStr"/>
-      <c r="K36" s="18" t="inlineStr"/>
+      <c r="K36" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] DONE: BuildReveal staggered framer-motion unveil of count tiles + workflow chips (BuildReveal.js:340-357).</t>
+        </is>
+      </c>
       <c r="L36" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -4126,7 +4235,11 @@
         </is>
       </c>
       <c r="J37" s="16" t="inlineStr"/>
-      <c r="K37" s="16" t="inlineStr"/>
+      <c r="K37" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: No post-onboarding AI-status banner, no /api/tenant/ai-setup/retry wiring (0 grep hits).</t>
+        </is>
+      </c>
       <c r="L37" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -4178,7 +4291,11 @@
         </is>
       </c>
       <c r="J38" s="18" t="inlineStr"/>
-      <c r="K38" s="18" t="inlineStr"/>
+      <c r="K38" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: No extracted OnboardingLayout w/ shared H1/subhead/CTA slots; interview type ramp diverges.</t>
+        </is>
+      </c>
       <c r="L38" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -4230,7 +4347,11 @@
         </is>
       </c>
       <c r="J39" s="16" t="inlineStr"/>
-      <c r="K39" s="16" t="inlineStr"/>
+      <c r="K39" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: Mobile onboarding walkthrough (iPhone SE/Pixel) not done - QA task.</t>
+        </is>
+      </c>
       <c r="L39" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -4282,7 +4403,11 @@
         </is>
       </c>
       <c r="J40" s="18" t="inlineStr"/>
-      <c r="K40" s="18" t="inlineStr"/>
+      <c r="K40" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: Desk narrative is a deterministic ranker (InsightWell), not LLM; LLM shape deferred to E3-06.</t>
+        </is>
+      </c>
       <c r="L40" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -4330,11 +4455,15 @@
       </c>
       <c r="I41" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="J41" s="16" t="inlineStr"/>
-      <c r="K41" s="16" t="inlineStr"/>
+      <c r="K41" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] DROP: Obsolete: Desk chip/filter row removed in KR-8, replaced by DecisionBento (sections sized by priority, no filter pills).</t>
+        </is>
+      </c>
       <c r="L41" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -4386,7 +4515,11 @@
         </is>
       </c>
       <c r="J42" s="18" t="inlineStr"/>
-      <c r="K42" s="18" t="inlineStr"/>
+      <c r="K42" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Trends deep-links carry filter params; target-screen active-chip-on-arrival still unverified.</t>
+        </is>
+      </c>
       <c r="L42" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -4438,7 +4571,11 @@
         </is>
       </c>
       <c r="J43" s="16" t="inlineStr"/>
-      <c r="K43" s="16" t="inlineStr"/>
+      <c r="K43" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Per-section empty copy calmer, but no coaching CTA (capture moved off Desk).</t>
+        </is>
+      </c>
       <c r="L43" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -4490,7 +4627,11 @@
         </is>
       </c>
       <c r="J44" s="18" t="inlineStr"/>
-      <c r="K44" s="18" t="inlineStr"/>
+      <c r="K44" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Mobile has always-on DexFab quick-capture; desktop Desk has none (moved to /brain). Desktop muscle-memory gap open.</t>
+        </is>
+      </c>
       <c r="L44" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -4542,7 +4683,11 @@
         </is>
       </c>
       <c r="J45" s="16" t="inlineStr"/>
-      <c r="K45" s="16" t="inlineStr"/>
+      <c r="K45" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: Section count badges visual-only, no explicit aria-label.</t>
+        </is>
+      </c>
       <c r="L45" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -4930,7 +5075,11 @@
         </is>
       </c>
       <c r="J52" s="18" t="inlineStr"/>
-      <c r="K52" s="18" t="inlineStr"/>
+      <c r="K52" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: KR-11 tightened spacing/glass well, but cards intentionally neumorphic (soft shadow), not flattened.</t>
+        </is>
+      </c>
       <c r="L52" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -4982,7 +5131,11 @@
         </is>
       </c>
       <c r="J53" s="16" t="inlineStr"/>
-      <c r="K53" s="16" t="inlineStr"/>
+      <c r="K53" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: Tasks capped at 4 w/ '+N more'; no per-card collapse/expand + localStorage memory.</t>
+        </is>
+      </c>
       <c r="L53" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -5034,7 +5187,11 @@
         </is>
       </c>
       <c r="J54" s="18" t="inlineStr"/>
-      <c r="K54" s="18" t="inlineStr"/>
+      <c r="K54" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: Reason dialog spartan; no char counter, prior-reasons dropdown, role suggestions.</t>
+        </is>
+      </c>
       <c r="L54" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -5082,11 +5239,15 @@
       </c>
       <c r="I55" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="J55" s="16" t="inlineStr"/>
-      <c r="K55" s="16" t="inlineStr"/>
+      <c r="K55" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] DROP: Decision settled: redesign committed to board-only kanban w/ drag-drop; no list view. Record as permanent.</t>
+        </is>
+      </c>
       <c r="L55" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -5134,11 +5295,15 @@
       </c>
       <c r="I56" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J56" s="18" t="inlineStr"/>
-      <c r="K56" s="18" t="inlineStr"/>
+      <c r="K56" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] DONE: Workflow labels from tenant.operating_model.pipelines[].label; lexicon.workflows retired (Workflows.js:327).</t>
+        </is>
+      </c>
       <c r="L56" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -5190,7 +5355,11 @@
         </is>
       </c>
       <c r="J57" s="16" t="inlineStr"/>
-      <c r="K57" s="16" t="inlineStr"/>
+      <c r="K57" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Stages advance via keyboard-operable Advance button; M+arrow keyboard-drag gesture not built.</t>
+        </is>
+      </c>
       <c r="L57" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -5238,11 +5407,15 @@
       </c>
       <c r="I58" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="J58" s="18" t="inlineStr"/>
-      <c r="K58" s="18" t="inlineStr"/>
+      <c r="K58" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] DROP: Done differently: Contacts merged into single CRM nav; /contacts redirects to /crm (Layout.js:63, App.js:133).</t>
+        </is>
+      </c>
       <c r="L58" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -5350,7 +5523,11 @@
         </is>
       </c>
       <c r="J60" s="18" t="inlineStr"/>
-      <c r="K60" s="18" t="inlineStr"/>
+      <c r="K60" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: CSV lands in editable review panel (fix-before-file); no per-row failure/error surfacing on partial import.</t>
+        </is>
+      </c>
       <c r="L60" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -5398,11 +5575,15 @@
       </c>
       <c r="I61" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J61" s="16" t="inlineStr"/>
-      <c r="K61" s="16" t="inlineStr"/>
+      <c r="K61" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] DONE: Relationship score shows reason sentence + signal chips, desktop + mobile (ContactProfile.js:280-287).</t>
+        </is>
+      </c>
       <c r="L61" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -5510,7 +5691,11 @@
         </is>
       </c>
       <c r="J63" s="16" t="inlineStr"/>
-      <c r="K63" s="16" t="inlineStr"/>
+      <c r="K63" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: CRM list/filters at parity on responsive tree; mobile profile AI intel read-only (no rescore/'Score with AI').</t>
+        </is>
+      </c>
       <c r="L63" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -5562,7 +5747,11 @@
         </is>
       </c>
       <c r="J64" s="18" t="inlineStr"/>
-      <c r="K64" s="18" t="inlineStr"/>
+      <c r="K64" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Revenue overdue callout shipped; Finance Overview still six equal-weight KPI tiles, no hero metric elevated (Ledger.js:542).</t>
+        </is>
+      </c>
       <c r="L64" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -5614,7 +5803,11 @@
         </is>
       </c>
       <c r="J65" s="16" t="inlineStr"/>
-      <c r="K65" s="16" t="inlineStr"/>
+      <c r="K65" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Insight cards have inline 'Ask AI' chip; not the context-routing 'Ask Dex about this' chip (E3-01).</t>
+        </is>
+      </c>
       <c r="L65" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -5666,7 +5859,11 @@
         </is>
       </c>
       <c r="J66" s="18" t="inlineStr"/>
-      <c r="K66" s="18" t="inlineStr"/>
+      <c r="K66" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: ReviewPanel not restructured; still on pre-rebrand tokens (brand-600/card-brutal) - only file untouched by karma.</t>
+        </is>
+      </c>
       <c r="L66" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -5718,7 +5915,11 @@
         </is>
       </c>
       <c r="J67" s="16" t="inlineStr"/>
-      <c r="K67" s="16" t="inlineStr"/>
+      <c r="K67" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: WhatsAppCard has generic forwarding one-liner; no reply-to-nudge explanation + example.</t>
+        </is>
+      </c>
       <c r="L67" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -5770,7 +5971,11 @@
         </is>
       </c>
       <c r="J68" s="18" t="inlineStr"/>
-      <c r="K68" s="18" t="inlineStr"/>
+      <c r="K68" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: Expenses flat table; no inline drawer revealing line items.</t>
+        </is>
+      </c>
       <c r="L68" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -5818,11 +6023,15 @@
       </c>
       <c r="I69" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="J69" s="16" t="inlineStr"/>
-      <c r="K69" s="16" t="inlineStr"/>
+      <c r="K69" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] DROP: Obsolete: FinanceMobile.jsx deleted in KR-10, unified responsive Ledger tree; camera receipt-scan present (Ledger.js:1170).</t>
+        </is>
+      </c>
       <c r="L69" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -5874,7 +6083,11 @@
         </is>
       </c>
       <c r="J70" s="18" t="inlineStr"/>
-      <c r="K70" s="18" t="inlineStr"/>
+      <c r="K70" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: DexBadge persona chip on /ask answers only; not an avatar, absent from WorkCoach/OperatingScore narratives.</t>
+        </is>
+      </c>
       <c r="L70" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -5926,7 +6139,11 @@
         </is>
       </c>
       <c r="J71" s="16" t="inlineStr"/>
-      <c r="K71" s="16" t="inlineStr"/>
+      <c r="K71" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: Dex answers don't stream (blocking); no Stop-generating/retry/copy controls.</t>
+        </is>
+      </c>
       <c r="L71" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -5978,7 +6195,11 @@
         </is>
       </c>
       <c r="J72" s="18" t="inlineStr"/>
-      <c r="K72" s="18" t="inlineStr"/>
+      <c r="K72" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: BrainDocuments search + kind filter shipped; preview-on-hover + 'ask Dex about doc' still missing.</t>
+        </is>
+      </c>
       <c r="L72" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -6030,7 +6251,11 @@
         </is>
       </c>
       <c r="J73" s="16" t="inlineStr"/>
-      <c r="K73" s="16" t="inlineStr"/>
+      <c r="K73" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Dex empty state shows example prompts, but static/generic, not industry-specific from operating_model.</t>
+        </is>
+      </c>
       <c r="L73" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -6082,7 +6307,11 @@
         </is>
       </c>
       <c r="J74" s="18" t="inlineStr"/>
-      <c r="K74" s="18" t="inlineStr"/>
+      <c r="K74" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: No ?context= URL param handling, no pinned/clearable context chip.</t>
+        </is>
+      </c>
       <c r="L74" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -6134,7 +6363,11 @@
         </is>
       </c>
       <c r="J75" s="16" t="inlineStr"/>
-      <c r="K75" s="16" t="inlineStr"/>
+      <c r="K75" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: No aria-live region on transcript preview; recording announces nothing to SR.</t>
+        </is>
+      </c>
       <c r="L75" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -6242,7 +6475,11 @@
         </is>
       </c>
       <c r="J77" s="16" t="inlineStr"/>
-      <c r="K77" s="16" t="inlineStr"/>
+      <c r="K77" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: WorkCoach improvements are text-only; no per-item coach/'working on' affordance.</t>
+        </is>
+      </c>
       <c r="L77" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -6294,7 +6531,11 @@
         </is>
       </c>
       <c r="J78" s="18" t="inlineStr"/>
-      <c r="K78" s="18" t="inlineStr"/>
+      <c r="K78" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Roster group headers use tenant role labels; member profile dialog still prints raw role key (Team.js:520).</t>
+        </is>
+      </c>
       <c r="L78" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -6346,7 +6587,11 @@
         </is>
       </c>
       <c r="J79" s="16" t="inlineStr"/>
-      <c r="K79" s="16" t="inlineStr"/>
+      <c r="K79" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: No shared ContactChip component; person card only reuses kr-bento primitive.</t>
+        </is>
+      </c>
       <c r="L79" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -6394,11 +6639,15 @@
       </c>
       <c r="I80" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="J80" s="18" t="inlineStr"/>
-      <c r="K80" s="18" t="inlineStr"/>
+      <c r="K80" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] DROP: Obsolete: no TeamMobile.jsx; redesign made Team.js responsive single-file; role edit in shared MemberDialog.</t>
+        </is>
+      </c>
       <c r="L80" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -6450,7 +6699,11 @@
         </is>
       </c>
       <c r="J81" s="16" t="inlineStr"/>
-      <c r="K81" s="16" t="inlineStr"/>
+      <c r="K81" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: Notifications flat list; no collapse-by-source + per-group unread (read-state persistence already works).</t>
+        </is>
+      </c>
       <c r="L81" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -6502,7 +6755,11 @@
         </is>
       </c>
       <c r="J82" s="18" t="inlineStr"/>
-      <c r="K82" s="18" t="inlineStr"/>
+      <c r="K82" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: No weekend zebra/muted-past; past days currently highlighted (opposite).</t>
+        </is>
+      </c>
       <c r="L82" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -6554,7 +6811,11 @@
         </is>
       </c>
       <c r="J83" s="16" t="inlineStr"/>
-      <c r="K83" s="16" t="inlineStr"/>
+      <c r="K83" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Leave request streamlined w/ validation+toast; two date inputs (no range picker), explicit Submit (no auto-submit).</t>
+        </is>
+      </c>
       <c r="L83" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -6606,7 +6867,11 @@
         </is>
       </c>
       <c r="J84" s="18" t="inlineStr"/>
-      <c r="K84" s="18" t="inlineStr"/>
+      <c r="K84" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: Journal decision entries title+chips only; no first-line content preview.</t>
+        </is>
+      </c>
       <c r="L84" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -6658,7 +6923,11 @@
         </is>
       </c>
       <c r="J85" s="16" t="inlineStr"/>
-      <c r="K85" s="16" t="inlineStr"/>
+      <c r="K85" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Notif bell synced badge + click-opens-panel + aria-label done; no auto-mark-read behavior.</t>
+        </is>
+      </c>
       <c r="L85" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -6710,7 +6979,11 @@
         </is>
       </c>
       <c r="J86" s="18" t="inlineStr"/>
-      <c r="K86" s="18" t="inlineStr"/>
+      <c r="K86" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: No Meetings recording surface; mic failure shows generic toast, no settings fallback.</t>
+        </is>
+      </c>
       <c r="L86" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -6762,7 +7035,11 @@
         </is>
       </c>
       <c r="J87" s="16" t="inlineStr"/>
-      <c r="K87" s="16" t="inlineStr"/>
+      <c r="K87" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: Lexicon editor exists (BusinessVocabulary) but no live-preview panel.</t>
+        </is>
+      </c>
       <c r="L87" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -6814,7 +7091,11 @@
         </is>
       </c>
       <c r="J88" s="18" t="inlineStr"/>
-      <c r="K88" s="18" t="inlineStr"/>
+      <c r="K88" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: OperatingModel side-effect param editor not built; only kind chips + delete.</t>
+        </is>
+      </c>
       <c r="L88" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -6866,7 +7147,11 @@
         </is>
       </c>
       <c r="J89" s="16" t="inlineStr"/>
-      <c r="K89" s="16" t="inlineStr"/>
+      <c r="K89" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Each settings section has Save button + toast; no per-section dirty/saved-state indicator.</t>
+        </is>
+      </c>
       <c r="L89" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -6918,7 +7203,11 @@
         </is>
       </c>
       <c r="J90" s="18" t="inlineStr"/>
-      <c r="K90" s="18" t="inlineStr"/>
+      <c r="K90" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: No 2FA/session UI to write copy for; feature absent in Account tab (premise stale).</t>
+        </is>
+      </c>
       <c r="L90" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -6970,7 +7259,11 @@
         </is>
       </c>
       <c r="J91" s="16" t="inlineStr"/>
-      <c r="K91" s="16" t="inlineStr"/>
+      <c r="K91" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: Settings forms mix label-above vs inline; no single enforced pattern.</t>
+        </is>
+      </c>
       <c r="L91" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -7022,7 +7315,11 @@
         </is>
       </c>
       <c r="J92" s="18" t="inlineStr"/>
-      <c r="K92" s="18" t="inlineStr"/>
+      <c r="K92" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: No SettingsMobile.jsx (now responsive Settings.js); 4-tab mobile render/save audit pending.</t>
+        </is>
+      </c>
       <c r="L92" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -7074,7 +7371,11 @@
         </is>
       </c>
       <c r="J93" s="16" t="inlineStr"/>
-      <c r="K93" s="16" t="inlineStr"/>
+      <c r="K93" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Admin overview already a metrics dashboard (8 tiles); lacks specific hero metrics (active-this-week, usage-$, tickets).</t>
+        </is>
+      </c>
       <c r="L93" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -7126,7 +7427,11 @@
         </is>
       </c>
       <c r="J94" s="18" t="inlineStr"/>
-      <c r="K94" s="18" t="inlineStr"/>
+      <c r="K94" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: Admin tenant list flat table; no search/filter/bulk-select.</t>
+        </is>
+      </c>
       <c r="L94" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -7178,7 +7483,11 @@
         </is>
       </c>
       <c r="J95" s="16" t="inlineStr"/>
-      <c r="K95" s="16" t="inlineStr"/>
+      <c r="K95" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Per-tenant + per-provider cost present as table+grid; no expand-row, AI-only (no SMS/storage split).</t>
+        </is>
+      </c>
       <c r="L95" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -7230,7 +7539,11 @@
         </is>
       </c>
       <c r="J96" s="18" t="inlineStr"/>
-      <c r="K96" s="18" t="inlineStr"/>
+      <c r="K96" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Delete-tenant confirm names blast radius + type-to-confirm; suspend/reset-access/AI-key save still unguarded.</t>
+        </is>
+      </c>
       <c r="L96" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -7282,7 +7595,11 @@
         </is>
       </c>
       <c r="J97" s="16" t="inlineStr"/>
-      <c r="K97" s="16" t="inlineStr"/>
+      <c r="K97" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: No keyboard-driven bulk actions in admin (depends on 13.2).</t>
+        </is>
+      </c>
       <c r="L97" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -7334,7 +7651,11 @@
         </is>
       </c>
       <c r="J98" s="18" t="inlineStr"/>
-      <c r="K98" s="18" t="inlineStr"/>
+      <c r="K98" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Full CSS-var token system live + 0 hardcoded shadows; ~90 hardcoded hex remain (mostly admin/* + Landing).</t>
+        </is>
+      </c>
       <c r="L98" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -7386,7 +7707,11 @@
         </is>
       </c>
       <c r="J99" s="16" t="inlineStr"/>
-      <c r="K99" s="16" t="inlineStr"/>
+      <c r="K99" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Fonts unified to one family; no documented H1..caption size scale, 114 arbitrary text-[px] across 27 files.</t>
+        </is>
+      </c>
       <c r="L99" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -7438,7 +7763,11 @@
         </is>
       </c>
       <c r="J100" s="18" t="inlineStr"/>
-      <c r="K100" s="18" t="inlineStr"/>
+      <c r="K100" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Default grid is 4pt-aligned but no --space-* token scale or enforcement/audit.</t>
+        </is>
+      </c>
       <c r="L100" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -7490,7 +7819,11 @@
         </is>
       </c>
       <c r="J101" s="16" t="inlineStr"/>
-      <c r="K101" s="16" t="inlineStr"/>
+      <c r="K101" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: App largely on @phosphor-icons (74 files); lucide persists in vendored shadcn ui/ primitives; emoji not swept.</t>
+        </is>
+      </c>
       <c r="L101" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -7542,7 +7875,11 @@
         </is>
       </c>
       <c r="J102" s="18" t="inlineStr"/>
-      <c r="K102" s="18" t="inlineStr"/>
+      <c r="K102" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: DesignLab + MobileKitchenSink dev harnesses exist; no formal colors/type/spacing/do-don't docs page.</t>
+        </is>
+      </c>
       <c r="L102" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -7594,7 +7931,11 @@
         </is>
       </c>
       <c r="J103" s="16" t="inlineStr"/>
-      <c r="K103" s="16" t="inlineStr"/>
+      <c r="K103" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Shared EmptyState in 16 pages/42 usages; not universal (Team/People/Tasks/Workflows thin).</t>
+        </is>
+      </c>
       <c r="L103" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -7646,7 +7987,11 @@
         </is>
       </c>
       <c r="J104" s="18" t="inlineStr"/>
-      <c r="K104" s="18" t="inlineStr"/>
+      <c r="K104" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Shaped skeletons on key pages (13 files); animate-spin still in ~17 files.</t>
+        </is>
+      </c>
       <c r="L104" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -7698,7 +8043,11 @@
         </is>
       </c>
       <c r="J105" s="16" t="inlineStr"/>
-      <c r="K105" s="16" t="inlineStr"/>
+      <c r="K105" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Retry/plain-language error copy across 19 files; no universal error component, coverage inconsistent.</t>
+        </is>
+      </c>
       <c r="L105" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -7750,7 +8099,11 @@
         </is>
       </c>
       <c r="J106" s="18" t="inlineStr"/>
-      <c r="K106" s="18" t="inlineStr"/>
+      <c r="K106" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Some contextual loading copy; generic 'Loading' still in 24 files, not systematically replaced.</t>
+        </is>
+      </c>
       <c r="L106" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -7802,7 +8155,11 @@
         </is>
       </c>
       <c r="J107" s="16" t="inlineStr"/>
-      <c r="K107" s="16" t="inlineStr"/>
+      <c r="K107" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: Automated UX audit harness exists but no axe-core/Lighthouse contrast pass.</t>
+        </is>
+      </c>
       <c r="L107" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -7854,7 +8211,11 @@
         </is>
       </c>
       <c r="J108" s="18" t="inlineStr"/>
-      <c r="K108" s="18" t="inlineStr"/>
+      <c r="K108" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Native tab order OK; custom widgets (kanban) still lack keyboard equivalents.</t>
+        </is>
+      </c>
       <c r="L108" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -7902,11 +8263,15 @@
       </c>
       <c r="I109" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J109" s="16" t="inlineStr"/>
-      <c r="K109" s="16" t="inlineStr"/>
+      <c r="K109" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] DONE: Single --focus-ring token both themes + global :focus-visible outline (index.css:520,681).</t>
+        </is>
+      </c>
       <c r="L109" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -7958,7 +8323,11 @@
         </is>
       </c>
       <c r="J110" s="18" t="inlineStr"/>
-      <c r="K110" s="18" t="inlineStr"/>
+      <c r="K110" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: aria-label 67 hits/28 files + live regions for toasts/skeletons; icon-only buttons not fully labeled, 2 leaked strings.</t>
+        </is>
+      </c>
       <c r="L110" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -8010,7 +8379,11 @@
         </is>
       </c>
       <c r="J111" s="16" t="inlineStr"/>
-      <c r="K111" s="16" t="inlineStr"/>
+      <c r="K111" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Touch-size tokens (44/48/56) + audit rule in place; baseline still flagged many 40x40 controls; current unverified.</t>
+        </is>
+      </c>
       <c r="L111" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -8058,11 +8431,15 @@
       </c>
       <c r="I112" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J112" s="18" t="inlineStr"/>
-      <c r="K112" s="18" t="inlineStr"/>
+      <c r="K112" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] DONE: prefers-reduced-motion in 7 CSS blocks + JS matchMedia guards (useReveal, Layout, CountUp).</t>
+        </is>
+      </c>
       <c r="L112" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -8114,7 +8491,11 @@
         </is>
       </c>
       <c r="J113" s="16" t="inlineStr"/>
-      <c r="K113" s="16" t="inlineStr"/>
+      <c r="K113" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Premise reframed: per-screen *Mobile.jsx obsolete - routes now responsive; remaining work is per-route mobile polish.</t>
+        </is>
+      </c>
       <c r="L113" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -8162,11 +8543,15 @@
       </c>
       <c r="I114" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J114" s="18" t="inlineStr"/>
-      <c r="K114" s="18" t="inlineStr"/>
+      <c r="K114" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] DONE: InstallPrompt 3rd-session dismissible coach-mark + iOS fallback (InstallPrompt.jsx, Layout.js:534).</t>
+        </is>
+      </c>
       <c r="L114" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -8214,11 +8599,15 @@
       </c>
       <c r="I115" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J115" s="16" t="inlineStr"/>
-      <c r="K115" s="16" t="inlineStr"/>
+      <c r="K115" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] DONE: Workbox SW NetworkFirst offline caching for read routes + offline.html; money POSTs refuse loudly (service-worker.js).</t>
+        </is>
+      </c>
       <c r="L115" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -8266,11 +8655,15 @@
       </c>
       <c r="I116" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J116" s="18" t="inlineStr"/>
-      <c r="K116" s="18" t="inlineStr"/>
+      <c r="K116" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] DONE: manifest indigo theme + 192/512 maskable icon set (manifest.json).</t>
+        </is>
+      </c>
       <c r="L116" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -8322,7 +8715,11 @@
         </is>
       </c>
       <c r="J117" s="16" t="inlineStr"/>
-      <c r="K117" s="16" t="inlineStr"/>
+      <c r="K117" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Some gestures have button equivalents (UndoSnackbar/BottomSheet); no comprehensive switch-control/keyboard parity pass.</t>
+        </is>
+      </c>
       <c r="L117" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -8374,7 +8771,11 @@
         </is>
       </c>
       <c r="J118" s="18" t="inlineStr"/>
-      <c r="K118" s="18" t="inlineStr"/>
+      <c r="K118" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Mostly i18n action-verb labels; 1 literal 'Submit' + widespread uppercase labels remain.</t>
+        </is>
+      </c>
       <c r="L118" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -8426,7 +8827,11 @@
         </is>
       </c>
       <c r="J119" s="16" t="inlineStr"/>
-      <c r="K119" s="16" t="inlineStr"/>
+      <c r="K119" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: No systematic top-20 error-message rewrite; raw system strings still leak (audit: 2 violations).</t>
+        </is>
+      </c>
       <c r="L119" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -8478,7 +8883,11 @@
         </is>
       </c>
       <c r="J120" s="18" t="inlineStr"/>
-      <c r="K120" s="18" t="inlineStr"/>
+      <c r="K120" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: Onboarding/Dex/WorkCoach voice consistency - copy audit, no artifact indicating done.</t>
+        </is>
+      </c>
       <c r="L120" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -8530,7 +8939,11 @@
         </is>
       </c>
       <c r="J121" s="16" t="inlineStr"/>
-      <c r="K121" s="16" t="inlineStr"/>
+      <c r="K121" s="16" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] PARTIAL: Confirm/Cancel/Discard vocab partly centralized in i18n but used ad-hoc across 24 files; no enforced pairing.</t>
+        </is>
+      </c>
       <c r="L121" s="16" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -8582,7 +8995,11 @@
         </is>
       </c>
       <c r="J122" s="18" t="inlineStr"/>
-      <c r="K122" s="18" t="inlineStr"/>
+      <c r="K122" s="18" t="inlineStr">
+        <is>
+          <t>[2026-08-20 karma-validation] KEEP: Epic 7 exit-gate E2E (desktop+iPhone SE+Pixel+tablet) not run - QA sign-off pending.</t>
+        </is>
+      </c>
       <c r="L122" s="18" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-17</t>
@@ -8700,7 +9117,8 @@
       </c>
       <c r="K124" s="13" t="inlineStr">
         <is>
-          <t>Wire target: HeroCard sparkline (U7-01.3 shipped as demo).</t>
+          <t>[2026-08-20 karma-validation] KEEP: BACKEND: no operating_score_history collection, no daily cron, no history endpoint.
+Wire target: HeroCard sparkline (U7-01.3 shipped as demo).</t>
         </is>
       </c>
       <c r="L124" s="13" t="inlineStr">
@@ -8760,7 +9178,8 @@
       </c>
       <c r="K125" s="13" t="inlineStr">
         <is>
-          <t>Wire target: HeroCard DeltaChip (U7-01.1 shipped as demo). Also enables per-employee deltas (U7-01.33).</t>
+          <t>[2026-08-20 karma-validation] KEEP: BACKEND: no week-over-week company.delta (needs history).
+Wire target: HeroCard DeltaChip (U7-01.1 shipped as demo). Also enables per-employee deltas (U7-01.33).</t>
         </is>
       </c>
       <c r="L125" s="13" t="inlineStr">
@@ -8820,7 +9239,8 @@
       </c>
       <c r="K126" s="13" t="inlineStr">
         <is>
-          <t>Wire target: CategoryCard drivers (U7-01.4 shipped as demo).</t>
+          <t>[2026-08-20 karma-validation] KEEP: BACKEND: no per-category drivers in payload; real tenants see blank driver rows.
+Wire target: CategoryCard drivers (U7-01.4 shipped as demo).</t>
         </is>
       </c>
       <c r="L126" s="13" t="inlineStr">
@@ -8880,7 +9300,8 @@
       </c>
       <c r="K127" s="13" t="inlineStr">
         <is>
-          <t>Wire target: CategoryDrillModal (U7-01.5..8 shipped as demo).</t>
+          <t>[2026-08-20 karma-validation] KEEP: BACKEND: no /operating-score/drill/{category} endpoint; real tenants get 'not wired' fallback.
+Wire target: CategoryDrillModal (U7-01.5..8 shipped as demo).</t>
         </is>
       </c>
       <c r="L127" s="13" t="inlineStr">
@@ -8940,7 +9361,8 @@
       </c>
       <c r="K128" s="13" t="inlineStr">
         <is>
-          <t>Wire targets: HeroCard narrative (U7-01.1) + DexExplainerCard (U7-01.9). Both shipped with hardcoded demo text.</t>
+          <t>[2026-08-20 karma-validation] KEEP: BACKEND: no /ai/operating-score-explain endpoint; Dex narrative demo-only.
+Wire targets: HeroCard narrative (U7-01.1) + DexExplainerCard (U7-01.9). Both shipped with hardcoded demo text.</t>
         </is>
       </c>
       <c r="L128" s="13" t="inlineStr">
@@ -9000,7 +9422,8 @@
       </c>
       <c r="K129" s="13" t="inlineStr">
         <is>
-          <t>Wire target: SuggestedActions chip row (U7-01.10 shipped as demo).</t>
+          <t>[2026-08-20 karma-validation] PARTIAL: Suggested-action chips now derive from real stats client-side (karmaScore.js:40); not a backend field; 'lift' estimate dropped as dishonest.
+Wire target: SuggestedActions chip row (U7-01.10 shipped as demo).</t>
         </is>
       </c>
       <c r="L129" s="13" t="inlineStr">
@@ -9060,7 +9483,8 @@
       </c>
       <c r="K130" s="13" t="inlineStr">
         <is>
-          <t>Wire target: Leaderboard per-row delta (U7-01.11 shipped as demo).</t>
+          <t>[2026-08-20 karma-validation] KEEP: BACKEND: no per-employee week-over-week delta; leaderboard shows no delta chip.
+Wire target: Leaderboard per-row delta (U7-01.11 shipped as demo).</t>
         </is>
       </c>
       <c r="L130" s="13" t="inlineStr">
@@ -9120,7 +9544,8 @@
       </c>
       <c r="K131" s="13" t="inlineStr">
         <is>
-          <t>Wire target: FormulaExplainer weights editor (U7-01.17 shipped as demo). Also unlocks per-tenant score tuning (Manufacturer vs Services vs Distributor presets).</t>
+          <t>[2026-08-20 karma-validation] KEEP: BACKEND: weights hardcoded, not read from tenant; FormulaExplainer editor local-only.
+Wire target: FormulaExplainer weights editor (U7-01.17 shipped as demo). Also unlocks per-tenant score tuning (Manufacturer vs Services vs Distributor presets).</t>
         </is>
       </c>
       <c r="L131" s="13" t="inlineStr">
@@ -9180,7 +9605,8 @@
       </c>
       <c r="K132" s="13" t="inlineStr">
         <is>
-          <t>Wire target: InlineCapture form (U7-01.15 shipped as demo).</t>
+          <t>[2026-08-20 karma-validation] KEEP: InlineCapture fake-sends; not wired to POST /api/voice-notes.
+Wire target: InlineCapture form (U7-01.15 shipped as demo).</t>
         </is>
       </c>
       <c r="L132" s="13" t="inlineStr">
@@ -9240,7 +9666,8 @@
       </c>
       <c r="K133" s="13" t="inlineStr">
         <is>
-          <t>Companion to U7-01.31 -- ship together to keep cost bounded.</t>
+          <t>[2026-08-20 karma-validation] KEEP: BACKEND: no 15-min per-tenant cache for explain endpoint (moot until 01.31).
+Companion to U7-01.31 -- ship together to keep cost bounded.</t>
         </is>
       </c>
       <c r="L133" s="13" t="inlineStr">
@@ -9300,7 +9727,8 @@
       </c>
       <c r="K134" s="13" t="inlineStr">
         <is>
-          <t>This is the analysis doc's Phase B in one item. Needs founder sign-off on formula shapes before implementation -- open decision #4.</t>
+          <t>[2026-08-20 karma-validation] KEEP: BACKEND: Phase B metric formulas not applied; responsiveness still penalizes overdue. Needs founder sign-off.
+This is the analysis doc's Phase B in one item. Needs founder sign-off on formula shapes before implementation -- open decision #4.</t>
         </is>
       </c>
       <c r="L134" s="13" t="inlineStr">
@@ -9360,7 +9788,8 @@
       </c>
       <c r="K135" s="13" t="inlineStr">
         <is>
-          <t>Wire target: U7-01.24 (frontend for the setting toggle + email template). Requires an email provider chosen and quota tracked.</t>
+          <t>[2026-08-20 karma-validation] KEEP: BACKEND: no weekly owner digest email cron/template.
+Wire target: U7-01.24 (frontend for the setting toggle + email template). Requires an email provider chosen and quota tracked.</t>
         </is>
       </c>
       <c r="L135" s="13" t="inlineStr">
@@ -9420,7 +9849,8 @@
       </c>
       <c r="K136" s="13" t="inlineStr">
         <is>
-          <t>Wire target: U7-01.25 (frontend share page + generator UI). Board-of-directors friendly one-pager, no auth needed.</t>
+          <t>[2026-08-20 karma-validation] KEEP: BACKEND: no signed-token public one-pager endpoint.
+Wire target: U7-01.25 (frontend share page + generator UI). Board-of-directors friendly one-pager, no auth needed.</t>
         </is>
       </c>
       <c r="L136" s="13" t="inlineStr">
@@ -10832,7 +11262,8 @@
       <c r="J161" s="16" t="n"/>
       <c r="K161" s="16" t="inlineStr">
         <is>
-          <t>Noted 2026-08-17 during the RD-5 sweep.</t>
+          <t>[2026-08-20 karma-validation] KEEP: Admin portal confirmed still on legacy theme (deliberate deferral).
+Noted 2026-08-17 during the RD-5 sweep.</t>
         </is>
       </c>
       <c r="L161" s="16" t="inlineStr">

--- a/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic7_UX_UI_Optimization.xlsx
@@ -1464,7 +1464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1497,6 +1497,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
@@ -2131,33 +2132,66 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Sprint 19</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Karma mobile pass — shipped</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>20</v>
+      </c>
+      <c r="D24" t="n">
+        <v>20</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>20 UI commits from karma-redesign (KR-14.2 desktop cleanup + KR-14.2-24 and KM-1..16 mobile pass). Every commit shipped to Backend_optimization via merge d810145 (2026-08-28).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Redesign log</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>KR/RD redesign changelog (shipped during rebuild)</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C25" t="n">
         <v>21</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D25" t="n">
         <v>22</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>See 'UI Redesign Log' sheet — 81 karma/RD/NM/MPWA UI commits, all shipped to Backend_optimization.</t>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>See 'UI Redesign Log' sheet — 105 karma / RD / NM / MPWA UI commits, all shipped to Backend_optimization. Sprint 19 carries the KM-* / KR-14.2-24 mobile pass entries in Backlog to keep the totals clean.</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4410,6 +4444,546 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Karma (final design language — shipped)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>bb1365c</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>KR-14.2 — the bento loses its fog and its dead air</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Karma mobile pass — shipped</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>a0b472c</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>KM-1 — mobile pass 1: /inbox reflow + shared foundation + 7 verified bugs</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Karma mobile pass — shipped</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>7df035a</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>KR-14.2–14.17 — the phone gets its own layout, the desktop is left alone</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Karma mobile pass — shipped</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>06947a3</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>KR-14.18–14.24 — mobile pass 2: desk KPI strip, workflow accordions, task expanded body</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Karma mobile pass — shipped</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>d230bf5</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>KM-3 — mobile pass 3: my-work, calendar, desk band, More panel, Dex voice</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Karma mobile pass — shipped</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>29cb4ef</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>KM-4 — /finance: all six tabs reachable, five tables become cards on a phone</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Karma mobile pass — shipped</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>25fe1fe</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>KM-5 — inbox card pill, my-work step gestures, calendar-free finance, dock menu</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Karma mobile pass — shipped</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>7cde42b</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>KM-6 — checklist strip, progress-only status bar, arrows back on step rows</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Karma mobile pass — shipped</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ca396f4</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>KM-7 — overdue pill row, one-row task actions, neumorphic plan editor, dock-width More</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Karma mobile pass — shipped</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>91a4c7e</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>KM-8 — the More menu goes light: no scrim, minimal glass, seven equal panes</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Karma mobile pass — shipped</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>5f04a36</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>KM-9 — More menu: no close button, fits its content, static tiles, slight dim</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Karma mobile pass — shipped</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>d780f7f</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>KM-9b — /inbox: progressive blur removed, band pulled clear of the dock</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Karma mobile pass — shipped</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>b128ee6</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>KM-10 — New Task dialog and contact profiles onto the neumorphic system</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Karma mobile pass — shipped</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>67b71c9</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>KM-10b — /journal rebuilt: neumorphic, calendar view + date picking</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Karma mobile pass — shipped</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0e08e2d</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>KM-11 — Dex moves into the bottom bar: ribbon wave + edge vignette</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Karma mobile pass — shipped</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>8fd0705</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>KM-12 — the decision review dialog joins the design system</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Karma mobile pass — shipped</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>b7f9441</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>KM-13 — /inbox takes the founder's glow artwork as its sky</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Karma mobile pass — shipped</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>b279883</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>KM-14 — the glow artwork is desktop-only; mobile keeps its gradient sky</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Karma mobile pass — shipped</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>6a34aa6</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>KM-15 — mobile /inbox takes the new glow artwork as a 9 KB WebP</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Karma mobile pass — shipped</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>b8f72a5</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>KM-16 — nudge the mobile glow so the grey core clears the greeting</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4421,7 +4995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L154"/>
+  <dimension ref="A1:L174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13150,13 +13724,1126 @@
         </is>
       </c>
     </row>
-    <row r="155" ht="70" customHeight="1"/>
-    <row r="156" ht="70" customHeight="1"/>
-    <row r="157" ht="70" customHeight="1"/>
-    <row r="158" ht="70" customHeight="1"/>
-    <row r="159" ht="70" customHeight="1"/>
-    <row r="160" ht="70" customHeight="1"/>
-    <row r="161" ht="70" customHeight="1"/>
+    <row r="155" ht="70" customHeight="1">
+      <c r="A155" s="16" t="inlineStr">
+        <is>
+          <t>U7-19.1</t>
+        </is>
+      </c>
+      <c r="B155" s="16" t="inlineStr">
+        <is>
+          <t>Desk (bento)</t>
+        </is>
+      </c>
+      <c r="C155" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D155" s="15" t="inlineStr">
+        <is>
+          <t>Karma polish</t>
+        </is>
+      </c>
+      <c r="E155" s="16" t="inlineStr">
+        <is>
+          <t>KR-14.2 · bento loses its fog and its dead air</t>
+        </is>
+      </c>
+      <c r="F155" s="16" t="inlineStr">
+        <is>
+          <t>Desktop bento clarity pass: killed the fog-veil overlay and reclaimed the dead air around the tiles.</t>
+        </is>
+      </c>
+      <c r="G155" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H155" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I155" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J155" s="16" t="n"/>
+      <c r="K155" s="16" t="inlineStr">
+        <is>
+          <t>Commit bb1365c. Landed on karma-redesign, merged into Backend_optimization via d810145.</t>
+        </is>
+      </c>
+      <c r="L155" s="16" t="inlineStr">
+        <is>
+          <t>karma-redesign (Chinmay) — recorded 2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="70" customHeight="1">
+      <c r="A156" s="16" t="inlineStr">
+        <is>
+          <t>U7-19.2</t>
+        </is>
+      </c>
+      <c r="B156" s="16" t="inlineStr">
+        <is>
+          <t>Mobile /inbox</t>
+        </is>
+      </c>
+      <c r="C156" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D156" s="15" t="inlineStr">
+        <is>
+          <t>Mobile pass</t>
+        </is>
+      </c>
+      <c r="E156" s="16" t="inlineStr">
+        <is>
+          <t>KM-1 · mobile pass 1: /inbox reflow + shared foundation</t>
+        </is>
+      </c>
+      <c r="F156" s="16" t="inlineStr">
+        <is>
+          <t>First real mobile pass on /inbox: reflow, shared mobile foundation module, 7 verified bugs squashed.</t>
+        </is>
+      </c>
+      <c r="G156" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H156" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I156" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J156" s="16" t="n"/>
+      <c r="K156" s="16" t="inlineStr">
+        <is>
+          <t>Commit a0b472c. Landed on karma-redesign, merged into Backend_optimization via d810145.</t>
+        </is>
+      </c>
+      <c r="L156" s="16" t="inlineStr">
+        <is>
+          <t>karma-redesign (Chinmay) — recorded 2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="70" customHeight="1">
+      <c r="A157" s="16" t="inlineStr">
+        <is>
+          <t>U7-19.3</t>
+        </is>
+      </c>
+      <c r="B157" s="16" t="inlineStr">
+        <is>
+          <t>Mobile shell (all pages)</t>
+        </is>
+      </c>
+      <c r="C157" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D157" s="15" t="inlineStr">
+        <is>
+          <t>Mobile pass</t>
+        </is>
+      </c>
+      <c r="E157" s="16" t="inlineStr">
+        <is>
+          <t>KR-14.2–14.17 · the phone gets its own layout, the desktop is left alone</t>
+        </is>
+      </c>
+      <c r="F157" s="16" t="inlineStr">
+        <is>
+          <t>16-step mobile layout: dedicated phone layout across the app while the desktop shell stays untouched.</t>
+        </is>
+      </c>
+      <c r="G157" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H157" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I157" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J157" s="16" t="n"/>
+      <c r="K157" s="16" t="inlineStr">
+        <is>
+          <t>Commit 7df035a. Landed on karma-redesign, merged into Backend_optimization via d810145.</t>
+        </is>
+      </c>
+      <c r="L157" s="16" t="inlineStr">
+        <is>
+          <t>karma-redesign (Chinmay) — recorded 2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="70" customHeight="1">
+      <c r="A158" s="16" t="inlineStr">
+        <is>
+          <t>U7-19.4</t>
+        </is>
+      </c>
+      <c r="B158" s="16" t="inlineStr">
+        <is>
+          <t>Mobile /desk, /workflows, /tasks</t>
+        </is>
+      </c>
+      <c r="C158" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D158" s="15" t="inlineStr">
+        <is>
+          <t>Mobile pass</t>
+        </is>
+      </c>
+      <c r="E158" s="16" t="inlineStr">
+        <is>
+          <t>KR-14.18–14.24 · mobile pass 2: desk KPI strip, workflow accordions, task expanded body</t>
+        </is>
+      </c>
+      <c r="F158" s="16" t="inlineStr">
+        <is>
+          <t>Mobile pass 2: mobile desk KPI strip, workflow board becomes accordions, task cards get an expanded body.</t>
+        </is>
+      </c>
+      <c r="G158" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H158" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I158" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J158" s="16" t="n"/>
+      <c r="K158" s="16" t="inlineStr">
+        <is>
+          <t>Commit 06947a3. Landed on karma-redesign, merged into Backend_optimization via d810145.</t>
+        </is>
+      </c>
+      <c r="L158" s="16" t="inlineStr">
+        <is>
+          <t>karma-redesign (Chinmay) — recorded 2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="70" customHeight="1">
+      <c r="A159" s="16" t="inlineStr">
+        <is>
+          <t>U7-19.5</t>
+        </is>
+      </c>
+      <c r="B159" s="16" t="inlineStr">
+        <is>
+          <t>Mobile /my-work, /calendar, dock</t>
+        </is>
+      </c>
+      <c r="C159" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D159" s="15" t="inlineStr">
+        <is>
+          <t>Mobile pass</t>
+        </is>
+      </c>
+      <c r="E159" s="16" t="inlineStr">
+        <is>
+          <t>KM-3 · mobile pass 3: my-work, calendar, desk band, More panel, Dex voice</t>
+        </is>
+      </c>
+      <c r="F159" s="16" t="inlineStr">
+        <is>
+          <t>Third mobile pass: my-work, calendar, desk band, More panel and Dex voice all reflowed.</t>
+        </is>
+      </c>
+      <c r="G159" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H159" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I159" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J159" s="16" t="n"/>
+      <c r="K159" s="16" t="inlineStr">
+        <is>
+          <t>Commit d230bf5. Landed on karma-redesign, merged into Backend_optimization via d810145.</t>
+        </is>
+      </c>
+      <c r="L159" s="16" t="inlineStr">
+        <is>
+          <t>karma-redesign (Chinmay) — recorded 2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="70" customHeight="1">
+      <c r="A160" s="16" t="inlineStr">
+        <is>
+          <t>U7-19.6</t>
+        </is>
+      </c>
+      <c r="B160" s="16" t="inlineStr">
+        <is>
+          <t>Mobile /finance</t>
+        </is>
+      </c>
+      <c r="C160" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D160" s="15" t="inlineStr">
+        <is>
+          <t>Mobile pass</t>
+        </is>
+      </c>
+      <c r="E160" s="16" t="inlineStr">
+        <is>
+          <t>KM-4 · /finance: all six tabs reachable, five tables become cards on a phone</t>
+        </is>
+      </c>
+      <c r="F160" s="16" t="inlineStr">
+        <is>
+          <t>Finance mobile: every one of the six tabs reachable on a phone, five tables rebuilt as card lists.</t>
+        </is>
+      </c>
+      <c r="G160" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H160" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I160" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J160" s="16" t="n"/>
+      <c r="K160" s="16" t="inlineStr">
+        <is>
+          <t>Commit 29cb4ef. Landed on karma-redesign, merged into Backend_optimization via d810145.</t>
+        </is>
+      </c>
+      <c r="L160" s="16" t="inlineStr">
+        <is>
+          <t>karma-redesign (Chinmay) — recorded 2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="70" customHeight="1">
+      <c r="A161" s="16" t="inlineStr">
+        <is>
+          <t>U7-19.7</t>
+        </is>
+      </c>
+      <c r="B161" s="16" t="inlineStr">
+        <is>
+          <t>/inbox card, my-work steps, /finance</t>
+        </is>
+      </c>
+      <c r="C161" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D161" s="15" t="inlineStr">
+        <is>
+          <t>Mobile pass</t>
+        </is>
+      </c>
+      <c r="E161" s="16" t="inlineStr">
+        <is>
+          <t>KM-5 · inbox card pill, my-work step gestures, calendar-free finance, dock menu</t>
+        </is>
+      </c>
+      <c r="F161" s="16" t="inlineStr">
+        <is>
+          <t>Inbox card pill, my-work step gestures, finance without the calendar surface, dock-driven menu.</t>
+        </is>
+      </c>
+      <c r="G161" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H161" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I161" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J161" s="16" t="n"/>
+      <c r="K161" s="16" t="inlineStr">
+        <is>
+          <t>Commit 25fe1fe. Landed on karma-redesign, merged into Backend_optimization via d810145.</t>
+        </is>
+      </c>
+      <c r="L161" s="16" t="inlineStr">
+        <is>
+          <t>karma-redesign (Chinmay) — recorded 2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="16" t="inlineStr">
+        <is>
+          <t>U7-19.8</t>
+        </is>
+      </c>
+      <c r="B162" s="16" t="inlineStr">
+        <is>
+          <t>Task detail, checklist</t>
+        </is>
+      </c>
+      <c r="C162" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D162" s="15" t="inlineStr">
+        <is>
+          <t>Mobile pass</t>
+        </is>
+      </c>
+      <c r="E162" s="16" t="inlineStr">
+        <is>
+          <t>KM-6 · checklist strip, progress-only status bar, arrows back on step rows</t>
+        </is>
+      </c>
+      <c r="F162" s="16" t="inlineStr">
+        <is>
+          <t>Checklist strip added, status bar becomes a progress track, back-arrows restored on step rows.</t>
+        </is>
+      </c>
+      <c r="G162" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H162" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I162" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J162" s="16" t="n"/>
+      <c r="K162" s="16" t="inlineStr">
+        <is>
+          <t>Commit 7cde42b. Landed on karma-redesign, merged into Backend_optimization via d810145.</t>
+        </is>
+      </c>
+      <c r="L162" s="16" t="inlineStr">
+        <is>
+          <t>karma-redesign (Chinmay) — recorded 2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="16" t="inlineStr">
+        <is>
+          <t>U7-19.9</t>
+        </is>
+      </c>
+      <c r="B163" s="16" t="inlineStr">
+        <is>
+          <t>Tasks, plan editor, More menu</t>
+        </is>
+      </c>
+      <c r="C163" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D163" s="15" t="inlineStr">
+        <is>
+          <t>Mobile pass</t>
+        </is>
+      </c>
+      <c r="E163" s="16" t="inlineStr">
+        <is>
+          <t>KM-7 · overdue pill row, one-row task actions, neumorphic plan editor, dock-width More</t>
+        </is>
+      </c>
+      <c r="F163" s="16" t="inlineStr">
+        <is>
+          <t>Overdue pill row, one-row task actions, plan editor rebuilt neumorphic, More menu takes dock width.</t>
+        </is>
+      </c>
+      <c r="G163" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H163" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I163" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J163" s="16" t="n"/>
+      <c r="K163" s="16" t="inlineStr">
+        <is>
+          <t>Commit ca396f4. Landed on karma-redesign, merged into Backend_optimization via d810145.</t>
+        </is>
+      </c>
+      <c r="L163" s="16" t="inlineStr">
+        <is>
+          <t>karma-redesign (Chinmay) — recorded 2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="16" t="inlineStr">
+        <is>
+          <t>U7-19.10</t>
+        </is>
+      </c>
+      <c r="B164" s="16" t="inlineStr">
+        <is>
+          <t>More menu</t>
+        </is>
+      </c>
+      <c r="C164" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D164" s="15" t="inlineStr">
+        <is>
+          <t>Mobile pass</t>
+        </is>
+      </c>
+      <c r="E164" s="16" t="inlineStr">
+        <is>
+          <t>KM-8 · More menu goes light — no scrim, minimal glass, seven equal panes</t>
+        </is>
+      </c>
+      <c r="F164" s="16" t="inlineStr">
+        <is>
+          <t>Light More menu: no scrim, minimal glass, seven equally-weighted panes.</t>
+        </is>
+      </c>
+      <c r="G164" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H164" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I164" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J164" s="16" t="n"/>
+      <c r="K164" s="16" t="inlineStr">
+        <is>
+          <t>Commit 91a4c7e. Landed on karma-redesign, merged into Backend_optimization via d810145.</t>
+        </is>
+      </c>
+      <c r="L164" s="16" t="inlineStr">
+        <is>
+          <t>karma-redesign (Chinmay) — recorded 2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="16" t="inlineStr">
+        <is>
+          <t>U7-19.11</t>
+        </is>
+      </c>
+      <c r="B165" s="16" t="inlineStr">
+        <is>
+          <t>More menu</t>
+        </is>
+      </c>
+      <c r="C165" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D165" s="15" t="inlineStr">
+        <is>
+          <t>Mobile pass</t>
+        </is>
+      </c>
+      <c r="E165" s="16" t="inlineStr">
+        <is>
+          <t>KM-9 · More menu — no close button, fits its content, static tiles, slight dim</t>
+        </is>
+      </c>
+      <c r="F165" s="16" t="inlineStr">
+        <is>
+          <t>More menu polish: close button removed, panel fits its content, tiles static, page dims slightly.</t>
+        </is>
+      </c>
+      <c r="G165" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H165" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I165" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J165" s="16" t="n"/>
+      <c r="K165" s="16" t="inlineStr">
+        <is>
+          <t>Commit 5f04a36. Landed on karma-redesign, merged into Backend_optimization via d810145.</t>
+        </is>
+      </c>
+      <c r="L165" s="16" t="inlineStr">
+        <is>
+          <t>karma-redesign (Chinmay) — recorded 2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="16" t="inlineStr">
+        <is>
+          <t>U7-19.12</t>
+        </is>
+      </c>
+      <c r="B166" s="16" t="inlineStr">
+        <is>
+          <t>/inbox, dock</t>
+        </is>
+      </c>
+      <c r="C166" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D166" s="15" t="inlineStr">
+        <is>
+          <t>Mobile pass</t>
+        </is>
+      </c>
+      <c r="E166" s="16" t="inlineStr">
+        <is>
+          <t>KM-9b · /inbox: progressive blur removed, band pulled clear of the dock</t>
+        </is>
+      </c>
+      <c r="F166" s="16" t="inlineStr">
+        <is>
+          <t>/inbox: killed progressive blur that muddied cards; band pulled clear of the dock overlap.</t>
+        </is>
+      </c>
+      <c r="G166" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H166" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I166" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J166" s="16" t="n"/>
+      <c r="K166" s="16" t="inlineStr">
+        <is>
+          <t>Commit d780f7f. Landed on karma-redesign, merged into Backend_optimization via d810145.</t>
+        </is>
+      </c>
+      <c r="L166" s="16" t="inlineStr">
+        <is>
+          <t>karma-redesign (Chinmay) — recorded 2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="16" t="inlineStr">
+        <is>
+          <t>U7-19.13</t>
+        </is>
+      </c>
+      <c r="B167" s="16" t="inlineStr">
+        <is>
+          <t>New Task dialog, contact profile</t>
+        </is>
+      </c>
+      <c r="C167" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D167" s="15" t="inlineStr">
+        <is>
+          <t>Mobile pass</t>
+        </is>
+      </c>
+      <c r="E167" s="16" t="inlineStr">
+        <is>
+          <t>KM-10 · New Task dialog and contact profiles onto the neumorphic system</t>
+        </is>
+      </c>
+      <c r="F167" s="16" t="inlineStr">
+        <is>
+          <t>New Task dialog and contact profile move onto the shared neumorphic system.</t>
+        </is>
+      </c>
+      <c r="G167" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H167" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I167" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J167" s="16" t="n"/>
+      <c r="K167" s="16" t="inlineStr">
+        <is>
+          <t>Commit b128ee6. Landed on karma-redesign, merged into Backend_optimization via d810145.</t>
+        </is>
+      </c>
+      <c r="L167" s="16" t="inlineStr">
+        <is>
+          <t>karma-redesign (Chinmay) — recorded 2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="16" t="inlineStr">
+        <is>
+          <t>U7-19.14</t>
+        </is>
+      </c>
+      <c r="B168" s="16" t="inlineStr">
+        <is>
+          <t>/journal</t>
+        </is>
+      </c>
+      <c r="C168" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D168" s="15" t="inlineStr">
+        <is>
+          <t>Mobile pass</t>
+        </is>
+      </c>
+      <c r="E168" s="16" t="inlineStr">
+        <is>
+          <t>KM-10b · /journal rebuilt — neumorphic, calendar view + date picking</t>
+        </is>
+      </c>
+      <c r="F168" s="16" t="inlineStr">
+        <is>
+          <t>/journal rebuilt on the neumorphic system with a calendar view and real date picking.</t>
+        </is>
+      </c>
+      <c r="G168" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H168" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I168" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J168" s="16" t="n"/>
+      <c r="K168" s="16" t="inlineStr">
+        <is>
+          <t>Commit 67b71c9. Landed on karma-redesign, merged into Backend_optimization via d810145.</t>
+        </is>
+      </c>
+      <c r="L168" s="16" t="inlineStr">
+        <is>
+          <t>karma-redesign (Chinmay) — recorded 2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="16" t="inlineStr">
+        <is>
+          <t>U7-19.15</t>
+        </is>
+      </c>
+      <c r="B169" s="16" t="inlineStr">
+        <is>
+          <t>Dex bottom-bar</t>
+        </is>
+      </c>
+      <c r="C169" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D169" s="15" t="inlineStr">
+        <is>
+          <t>Mobile pass</t>
+        </is>
+      </c>
+      <c r="E169" s="16" t="inlineStr">
+        <is>
+          <t>KM-11 · Dex moves into the bottom bar: ribbon wave + edge vignette</t>
+        </is>
+      </c>
+      <c r="F169" s="16" t="inlineStr">
+        <is>
+          <t>Dex moves into the bottom bar; adds ribbon-wave listening motion and an edge vignette.</t>
+        </is>
+      </c>
+      <c r="G169" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H169" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I169" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J169" s="16" t="n"/>
+      <c r="K169" s="16" t="inlineStr">
+        <is>
+          <t>Commit 0e08e2d. Landed on karma-redesign, merged into Backend_optimization via d810145.</t>
+        </is>
+      </c>
+      <c r="L169" s="16" t="inlineStr">
+        <is>
+          <t>karma-redesign (Chinmay) — recorded 2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="16" t="inlineStr">
+        <is>
+          <t>U7-19.16</t>
+        </is>
+      </c>
+      <c r="B170" s="16" t="inlineStr">
+        <is>
+          <t>Decision review dialog</t>
+        </is>
+      </c>
+      <c r="C170" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D170" s="15" t="inlineStr">
+        <is>
+          <t>Mobile pass</t>
+        </is>
+      </c>
+      <c r="E170" s="16" t="inlineStr">
+        <is>
+          <t>KM-12 · the decision review dialog joins the design system</t>
+        </is>
+      </c>
+      <c r="F170" s="16" t="inlineStr">
+        <is>
+          <t>The decision review dialog is brought onto the karma design system.</t>
+        </is>
+      </c>
+      <c r="G170" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H170" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I170" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J170" s="16" t="n"/>
+      <c r="K170" s="16" t="inlineStr">
+        <is>
+          <t>Commit 8fd0705. Landed on karma-redesign, merged into Backend_optimization via d810145.</t>
+        </is>
+      </c>
+      <c r="L170" s="16" t="inlineStr">
+        <is>
+          <t>karma-redesign (Chinmay) — recorded 2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="16" t="inlineStr">
+        <is>
+          <t>U7-19.17</t>
+        </is>
+      </c>
+      <c r="B171" s="16" t="inlineStr">
+        <is>
+          <t>/inbox background</t>
+        </is>
+      </c>
+      <c r="C171" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D171" s="15" t="inlineStr">
+        <is>
+          <t>Mobile pass</t>
+        </is>
+      </c>
+      <c r="E171" s="16" t="inlineStr">
+        <is>
+          <t>KM-13 · /inbox takes the founder's glow artwork as its sky</t>
+        </is>
+      </c>
+      <c r="F171" s="16" t="inlineStr">
+        <is>
+          <t>The founder-supplied glow artwork is adopted as /inbox's ambient sky.</t>
+        </is>
+      </c>
+      <c r="G171" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H171" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I171" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J171" s="16" t="n"/>
+      <c r="K171" s="16" t="inlineStr">
+        <is>
+          <t>Commit b7f9441. Landed on karma-redesign, merged into Backend_optimization via d810145.</t>
+        </is>
+      </c>
+      <c r="L171" s="16" t="inlineStr">
+        <is>
+          <t>karma-redesign (Chinmay) — recorded 2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="16" t="inlineStr">
+        <is>
+          <t>U7-19.18</t>
+        </is>
+      </c>
+      <c r="B172" s="16" t="inlineStr">
+        <is>
+          <t>/inbox background (desktop)</t>
+        </is>
+      </c>
+      <c r="C172" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D172" s="15" t="inlineStr">
+        <is>
+          <t>Mobile pass</t>
+        </is>
+      </c>
+      <c r="E172" s="16" t="inlineStr">
+        <is>
+          <t>KM-14 · glow artwork is desktop-only; mobile keeps its gradient sky</t>
+        </is>
+      </c>
+      <c r="F172" s="16" t="inlineStr">
+        <is>
+          <t>Restricted the glow artwork to desktop only; mobile keeps its lighter gradient sky.</t>
+        </is>
+      </c>
+      <c r="G172" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H172" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I172" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J172" s="16" t="n"/>
+      <c r="K172" s="16" t="inlineStr">
+        <is>
+          <t>Commit b279883. Landed on karma-redesign, merged into Backend_optimization via d810145.</t>
+        </is>
+      </c>
+      <c r="L172" s="16" t="inlineStr">
+        <is>
+          <t>karma-redesign (Chinmay) — recorded 2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="16" t="inlineStr">
+        <is>
+          <t>U7-19.19</t>
+        </is>
+      </c>
+      <c r="B173" s="16" t="inlineStr">
+        <is>
+          <t>/inbox mobile background</t>
+        </is>
+      </c>
+      <c r="C173" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D173" s="15" t="inlineStr">
+        <is>
+          <t>Mobile pass</t>
+        </is>
+      </c>
+      <c r="E173" s="16" t="inlineStr">
+        <is>
+          <t>KM-15 · mobile /inbox takes the new glow artwork as a 9 KB WebP</t>
+        </is>
+      </c>
+      <c r="F173" s="16" t="inlineStr">
+        <is>
+          <t>Mobile /inbox takes the new glow artwork shipped as a 9 KB WebP asset.</t>
+        </is>
+      </c>
+      <c r="G173" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H173" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I173" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J173" s="16" t="n"/>
+      <c r="K173" s="16" t="inlineStr">
+        <is>
+          <t>Commit 6a34aa6. Landed on karma-redesign, merged into Backend_optimization via d810145.</t>
+        </is>
+      </c>
+      <c r="L173" s="16" t="inlineStr">
+        <is>
+          <t>karma-redesign (Chinmay) — recorded 2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="16" t="inlineStr">
+        <is>
+          <t>U7-19.20</t>
+        </is>
+      </c>
+      <c r="B174" s="16" t="inlineStr">
+        <is>
+          <t>/inbox mobile background</t>
+        </is>
+      </c>
+      <c r="C174" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D174" s="15" t="inlineStr">
+        <is>
+          <t>Mobile pass</t>
+        </is>
+      </c>
+      <c r="E174" s="16" t="inlineStr">
+        <is>
+          <t>KM-16 · nudge the mobile glow so the grey core clears the greeting</t>
+        </is>
+      </c>
+      <c r="F174" s="16" t="inlineStr">
+        <is>
+          <t>Nudged the mobile glow so its grey core clears the greeting text underneath.</t>
+        </is>
+      </c>
+      <c r="G174" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H174" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I174" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J174" s="16" t="n"/>
+      <c r="K174" s="16" t="inlineStr">
+        <is>
+          <t>Commit b8f72a5. Landed on karma-redesign, merged into Backend_optimization via d810145.</t>
+        </is>
+      </c>
+      <c r="L174" s="16" t="inlineStr">
+        <is>
+          <t>karma-redesign (Chinmay) — recorded 2026-08-28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
